--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/giinhancom_0513/txt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF85DF2-3ED5-FB46-B872-E8D62E52A8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEF8636-3CF6-E546-BDB3-30B5E5B87147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6160" yWindow="2800" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="940" yWindow="680" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="196">
   <si>
     <t>category</t>
   </si>
@@ -277,6 +277,435 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>파타고니아</t>
+  </si>
+  <si>
+    <t>언마켓</t>
+  </si>
+  <si>
+    <t>탄소중립</t>
+  </si>
+  <si>
+    <t>돌고래전시</t>
+  </si>
+  <si>
+    <t>거북파티</t>
+  </si>
+  <si>
+    <t>적정거리</t>
+  </si>
+  <si>
+    <t>성원상회</t>
+  </si>
+  <si>
+    <t>SSFP</t>
+  </si>
+  <si>
+    <t>바이킹스</t>
+  </si>
+  <si>
+    <t>오늘전통</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>우유부단</t>
+  </si>
+  <si>
+    <t>호수</t>
+  </si>
+  <si>
+    <t>크라운제약</t>
+  </si>
+  <si>
+    <t>그렝이</t>
+  </si>
+  <si>
+    <t>엠펍</t>
+  </si>
+  <si>
+    <t>버스</t>
+  </si>
+  <si>
+    <t>의자전시</t>
+  </si>
+  <si>
+    <t>영디자이너</t>
+  </si>
+  <si>
+    <t>해녀</t>
+  </si>
+  <si>
+    <t>의성마르쉐</t>
+  </si>
+  <si>
+    <t>관광두레</t>
+  </si>
+  <si>
+    <t>이니스프리</t>
+  </si>
+  <si>
+    <t>츠루</t>
+  </si>
+  <si>
+    <t>파머스파티</t>
+  </si>
+  <si>
+    <t>세카</t>
+  </si>
+  <si>
+    <t>옥계시장</t>
+  </si>
+  <si>
+    <t>주문진그림</t>
+  </si>
+  <si>
+    <t>복어</t>
+  </si>
+  <si>
+    <t>꽃친</t>
+  </si>
+  <si>
+    <t>카라가이드</t>
+  </si>
+  <si>
+    <t>재단달력</t>
+  </si>
+  <si>
+    <t>유인원전시</t>
+  </si>
+  <si>
+    <t>하뮤페</t>
+  </si>
+  <si>
+    <t>위기이이웃들</t>
+  </si>
+  <si>
+    <t>ㄴㅋㄴㅋ</t>
+  </si>
+  <si>
+    <t>혜성</t>
+  </si>
+  <si>
+    <t>재단일</t>
+  </si>
+  <si>
+    <t>동축반축</t>
+  </si>
+  <si>
+    <t>쓰동시</t>
+  </si>
+  <si>
+    <t>파절이</t>
+  </si>
+  <si>
+    <t>캔</t>
+  </si>
+  <si>
+    <t>유인원굿즈</t>
+  </si>
+  <si>
+    <t>팩토리얼라이브</t>
+  </si>
+  <si>
+    <t>신세계</t>
+  </si>
+  <si>
+    <t>철새마을</t>
+  </si>
+  <si>
+    <t>부엉이</t>
+  </si>
+  <si>
+    <t>서초미식</t>
+  </si>
+  <si>
+    <t>액션러닝</t>
+  </si>
+  <si>
+    <t>동네서울</t>
+  </si>
+  <si>
+    <t>서초로컬</t>
+  </si>
+  <si>
+    <t>두루두루</t>
+  </si>
+  <si>
+    <t>에디션서촌</t>
+  </si>
+  <si>
+    <t>농가브랜딩</t>
+  </si>
+  <si>
+    <t>공주</t>
+  </si>
+  <si>
+    <t>아아침</t>
+  </si>
+  <si>
+    <t>도넛</t>
+  </si>
+  <si>
+    <t>손잡브</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>작브살</t>
+  </si>
+  <si>
+    <t>코리아나</t>
+  </si>
+  <si>
+    <t>제일기획</t>
+  </si>
+  <si>
+    <t>지큐</t>
+  </si>
+  <si>
+    <t>온라인 클래스</t>
+  </si>
+  <si>
+    <t>상상캠퍼스</t>
+  </si>
+  <si>
+    <t>춘천관광</t>
+  </si>
+  <si>
+    <t>선화예고</t>
+  </si>
+  <si>
+    <t>울산</t>
+  </si>
+  <si>
+    <t>WBC</t>
+  </si>
+  <si>
+    <t>서울예대</t>
+  </si>
+  <si>
+    <t>집중실험실</t>
+  </si>
+  <si>
+    <t>스토리스튜디오</t>
+  </si>
+  <si>
+    <t>고려대</t>
+  </si>
+  <si>
+    <t>전주센터</t>
+  </si>
+  <si>
+    <t>비마이비</t>
+  </si>
+  <si>
+    <t>에딧시티</t>
+  </si>
+  <si>
+    <t>곡성특강</t>
+  </si>
+  <si>
+    <t>북토크</t>
+  </si>
+  <si>
+    <t>뉴그라운드</t>
+  </si>
+  <si>
+    <t>서초도서관</t>
+  </si>
+  <si>
+    <t>고대크리켓</t>
+  </si>
+  <si>
+    <t>넥젠</t>
+  </si>
+  <si>
+    <t>질문의진화</t>
+  </si>
+  <si>
+    <t>서디창업센터</t>
+  </si>
+  <si>
+    <t>리부트</t>
+  </si>
+  <si>
+    <t>오풍카라</t>
+  </si>
+  <si>
+    <t>청양맛포럼</t>
+  </si>
+  <si>
+    <t>ㅂㅔ러로컬</t>
+  </si>
+  <si>
+    <t>골목창업학교</t>
+  </si>
+  <si>
+    <t>신보특강</t>
+  </si>
+  <si>
+    <t>지브인</t>
+  </si>
+  <si>
+    <t>헤그스킬업</t>
+  </si>
+  <si>
+    <t>유한양행</t>
+  </si>
+  <si>
+    <t>언독GS</t>
+  </si>
+  <si>
+    <t>강화유유</t>
+  </si>
+  <si>
+    <t>여성민우회</t>
+  </si>
+  <si>
+    <t>컨셉진</t>
+  </si>
+  <si>
+    <t>뉴웨이즈</t>
+  </si>
+  <si>
+    <t>브랜드액티비즘</t>
+  </si>
+  <si>
+    <t>넥스트로컬</t>
+  </si>
+  <si>
+    <t>춘천일기</t>
+  </si>
+  <si>
+    <t>한국의서원</t>
+  </si>
+  <si>
+    <t>헤이그라운드</t>
+  </si>
+  <si>
+    <t>아르떼</t>
+  </si>
+  <si>
+    <t>언독드림위드</t>
+  </si>
+  <si>
+    <t>환경연합오풍</t>
+  </si>
+  <si>
+    <t>고민상담소</t>
+  </si>
+  <si>
+    <t>남양주</t>
   </si>
 </sst>
 </file>
@@ -706,348 +1135,1134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.6640625" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.6640625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="5"/>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="2">
         <v>2</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="2">
         <v>3</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="3" t="s">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="3" t="s">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" s="2">
         <v>4</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="3" t="s">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="3" t="s">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="3" t="s">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" s="2">
         <v>5</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="3" t="s">
+    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="3" t="s">
+    <row r="104" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="3" t="s">
+    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2:C47 C48:C58 C59:C100 C101:C109" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A99FF-05B0-5848-80F4-332576867D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B7AEF-BCC0-CD4E-B35F-14D8D1569855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="680" windowWidth="32340" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="460" yWindow="680" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="273">
   <si>
     <t>category</t>
   </si>
@@ -645,6 +645,21 @@
 기획 &amp; 디자인 | 한지인
 일러스트레이션 | 홍민아
 사진 | 김진솔</t>
+  </si>
+  <si>
+    <t>성동구 일대에는 오랫동안 우리나라의 봉제산업의 뒤를 튼튼하게 뒷받침해 오던 봉제공장 지대가 곳곳에 자리하고 있습니다. 성동 지역의 기반 사업이라 부를 수 있는 패션봉제업을 중심으로 서울시와 성동구가 협력하여 로컬 중심의 소셜패션 생태계를 구축하는 다년간의 사업인 &lt;성수소셜패션프로젝트&gt;를 만들었습니다. 성동구 봉제공장의 잉여 원단을 활용하여 SSFP 브랜드의 상품으로 개발하는 화제성 프로젝트부터 본 사업의 장기적 성공을 위한 방법론 디자인까지 함께하며 성동 지역의 근본과 현재, 미래를 통합적으로 고민하고 결과물을 낼 수 있었던 시간이었습니다.
+성수소셜패션프로젝트 페이스북 페이지
+https://www.facebook.com/socialfashiondesign/
+프로덕트 디렉터 | 이경재 [대지를 위한 바느질]
+브랜딩 디렉터 | 한지인 [리메이크소사이어티]
+브랜딩 어시스턴트 | 최수경, 이수영
+프로젝트 브랜드 패션 디자이너 | 이규원
+연구 수행 책임자 | 김아미
+사진 | 김진솔
+전시 설치 | 중앙대학교 최수경 외
+협력 | 한국패션사회적협동조합, 나눔봉제협동조합, 성동패션봉제협동조합, 꿈한타래협동조합, 물레마실협동조합,
+아트그라운드협동조합, 라잇루트, 떳다할매, 금호고등학교 봉제동아리, 금호고등학교 학부모 봉제 모임
+ </t>
   </si>
   <si>
     <t>한국공예디자인문화진흥원 KCDF 에서 오랜 기간 지원해 오고 있던 ‘전통문화 청년창업육성 지원사업’의 리브랜딩 작업에 참여하여 기획과 리서치, 네이밍, 슬로건, 컨텐츠 라이팅 등의 업무를 맡아 진행했습니다. 유의미한 전통에 집중하면서, 더 다양하고 많은 사람들을 만나며 활동하고 싶은 청년 사업가들의 이야기를 수집하고 인사이트를 추출할 수 있었습니다.
@@ -943,17 +958,133 @@
 디자인 | 한지인</t>
   </si>
   <si>
-    <t>성동구 일대에는 오랫동안 우리나라의 봉제산업의 뒤를 튼튼하게 뒷받침해 오던 봉제공장 지대가 곳곳에 자리하고 있습니다. 성동 지역의 기반 사업이라 부를 수 있는 패션봉제업을 중심으로 서울시와 성동구가 협력하여 로컬 중심의 소셜패션 생태계를 구축하는 다년간의 사업인 &lt;성수소셜패션프로젝트&gt;를 만들었습니다. 성동구 봉제공장의 잉여 원단을 활용하여 SSFP 브랜드의 상품으로 개발하는 화제성 프로젝트부터 본 사업의 장기적 성공을 위한 방법론 디자인까지 함께하며 성동 지역의 근본과 현재, 미래를 통합적으로 고민하고 결과물을 낼 수 있었던 시간이었습니다.
-성수소셜패션프로젝트 페이스북 페이지
-https://www.facebook.com/socialfashiondesign/
-프로덕트 디렉터 | 이경재 [대지를 위한 바느질]
-브랜딩 디렉터 | 한지인 [리메이크소사이어티]
-브랜딩 어시스턴트 | 최수경, 이수영
-프로젝트 브랜드 패션 디자이너 | 이규원
-연구 수행 책임자 | 김아미
-사진 | 김진솔
-전시 설치 | 중앙대학교 최수경 외
-협력 | 한국패션사회적협동조합, 나눔봉제협동조합, 성동패션봉제협동조합, 꿈한타래협동조합, 물레마실협동조합, 아트그라운드협동조합, 라잇루트, 떳다할매, 금호고등학교 봉제동아리, 금호고등학교 학부모 봉제 모임</t>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2024, 2025</t>
+  </si>
+  <si>
+    <t>2009-2011</t>
+  </si>
+  <si>
+    <t>‘이야기와 동물과 시’를 떠드는 창작집단 way 의 입체물 작업자로 활동했습니다. 첫 공동 창작물인 ‘위기의 이웃’은 인간 사회에서 위기라고 불리울만한 특징을 멸종위기동물의 캐릭터와 결합시켜 웃음과 해학을 의도한 이야기 시리즈물입니다. 이야기에 등장하는 다양한 동물 캐릭터를 피규어, 천 인형, 나무 조각 등 다양한 재료와 표정으로 제작하는 일을 전담했습니다. 캐릭터를 활용한 수건을 제작, 굿즈로 판매하는 일 또한 진행했습니다.
+기계치, 소심, 완벽주의, 의심, 자기세계, 자학, 작심삼일, 잠수, 좋은오빠, 지름신, 팔랑귀가 각각 하나의 이야기로 제작되었습니다.
+글 | 김산하
+그림 | 김한민
+편집디자인 | 이수연
+영상 | 김도형, 박세준
+입체물 제작 | 한지인</t>
+  </si>
+  <si>
+    <t>위기의 이웃
+way studio</t>
+  </si>
+  <si>
+    <t>제주 유인원 필드스테이션에서 열린 하울링뮤직페스티벌에서 동물이 될 수 있는 분장을 만들었습니다. 2024년에는 참여 뮤지션의 동물 분장을 직접 만들어 제공하고, 축제에 온 친구들과 함께 평화의 날 퍼레이드를 위한 나만의 분장품을 만드는 워크샵을 진행했습니다. 2025년에는 축제에 온 친구들이 직접 준비해 온 안쓰는 물건, 헌 옷 등을 활용하여 ‘나만의 동물꼬리’를 만들어 달아주는 제작 부스를 운영했습니다.
+‘동물이 되기’는 존경하는 조애나 메이시 Joanna Macy 의 ‘모든 것의 협의회 Council of All beings’에서 아이디어를 착안한 활동으로 2025년 유인원 필드스테이션에서 선보인 전시, 워크샵의 핵심이 되는 가치와도 맞닿아 있습니다.
+2024 하울링 뮤직 페스티벌 소개
+https://www.instagram.com/p/C_0joPCyO5D/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+2025 하울링 페스티벌 소개
+https://www.instagram.com/p/DOKgkjrE2Ej/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+진행 | 하울링 페스티벌 기획단
+동물 분장 뮤지션 | 사이, 양양, 그레이스, 공룡 + 기획단 귀뚜라미
+제작 | 한지인</t>
+  </si>
+  <si>
+    <t>동물 머리랑 꼬리
+하울링 뮤직 페스티벌</t>
+  </si>
+  <si>
+    <t>동물학자가 만든 카페 유인원 필드스테이션의 전시실에서 직접 관찰한 자연을 그린 그림을 선보였습니다. 매달 제주를 방문해 변화하는 모습을 담고, 매달 워크샵을 열어 참가자들과 함께 관찰, 그림, 도감찾기를 진행했습니다. 
+“오랫동안 지켜보는 것에는 지루함이 필요합니다. 그렇게 기어이 무언가의 가까운 곳에서 오랫동안 한 곳을 쳐다보면 언젠가는 감탄의 순간이 다가옵니다. 쭈그리고 앉아 웅크려있던 시간이 뿌듯합니다.
+유인원 마당에서 살고 있는 친구들을 찾아봅니다. 매순간 수많은 이야기가 숨어있고, 떨어지고, 기어가고, 날아다니는 곳. 푹신한 풀숲과 든든한 돌 사이마다 곳곳에서 크고 작은 숨이 쉬어지고 있습니다. 모든 흔한 녹색과 갈색 사이에는 원대한 꿈과 비밀이 작용하고 있습니다.
+지루해질수록 더 큰 감탄을 만납니다.
+저는 이보다 더 즐거운 삶의 방식을 아직까지 만나지 못했습니다.”
+전시 소개
+https://www.instagram.com/p/DJn3HCbyidO/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+자연과 글그림 워크샵 소개
+https://www.instagram.com/p/DIyASpOyu4S/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Inspiring Boredom
+유인원 필드스테이션 생태전시</t>
+  </si>
+  <si>
+    <t>이화여대 에코과학부 동물행동생태연구실의 녹색과학통역프로젝트에서 관련 인사들에게 선물하는 달력을 디자인, 제작했습니다. 데이비드 아텐보로 David Attenborough 의 사진집 Life on Earth 속 눈길을 끄는 동물들을 선택해 직접 인형과 조형물로 만들어 촬영한 사진을 활용하여 나무와 종이의 2종으로 만든 거치대를 조립하였습니다. 월드디자인마켓 2009에 출품하여 판매하기도 하였습니다.
+진행 | 녹색과학통역프로젝트
+기획 제작 디자인 | 한지인</t>
+  </si>
+  <si>
+    <t>Life on Earth
+녹색과학통역프로젝트 달력</t>
+  </si>
+  <si>
+    <t>동물권행동 카라가 2020년 미디어 속 동물의 안전과 권리를 위해 제작한 국내 최초의 동물 출연 미디어 가이드라인의 버벌브랜딩과 에디터 작업으로 함께 했습니다. 카라 가이드라인은 국내 제작사들에게 배포, 활용되고 있으며 국내 방송사가 동물 출연 조항 및 가이드라인을 신설하는 것에 기여하였습니다.
+카라 미디어 가이드라인 소개와 다운로드
+https://saff.kr/we-animal/어떠한-동물도-해를-입지-않았습니다/
+디자인 스튜디오 오늘의 풍경의 프로젝트 후기
+https://blog.sceneryoftoday.kr/kara-union/
+기획 | 동물권행동 카라
+집필 | 동물권행동 카라, 동물권연구변호사단체 PNR
+네이밍 &amp; 편집 | 한지인
+디자인 | 오늘의풍경</t>
+  </si>
+  <si>
+    <t>어떠한 동물도 해를 입지 않았습니다
+카라 동물 출연 미디어 가이드라인</t>
+  </si>
+  <si>
+    <t>청소년 갭이어를 선택한 당사자와 가족이 모여있는 단체인 꽃다운친구들을 위한 아이덴티티를 디자인했습니다. 생동감있고 파릇파릇한 분위기를 내기 위한 작업을 진행했습니다.
+꽃다운친구들 공식페이지
+https://www.kochin.kr
+진행 | 꽃다운친구들 이예지
+디자인 | 한지인</t>
+  </si>
+  <si>
+    <t>꽃다운 친구들
+아이덴티티 디자인</t>
+  </si>
+  <si>
+    <t>주문진 수산시장의 한겨울 큰 잔치인 복어축제를 위한 브랜딩 및 제작 작업을 진행했습니다. 가시성이 높은 축제의 색상을 지정하고, 복어를 간결하면서도 다양하게 표현하는 방식으로 작업의 방향성을 잡아 기억에 나는 활력있는 축제가 되기를 바랐습니다.
+기획 진행 | 감자꽃 스튜디오
+브랜딩 | 한지인</t>
+  </si>
+  <si>
+    <t>복어축제 브랜딩
+주문진 수산시장</t>
+  </si>
+  <si>
+    <t>다채롭고 풍부한 자연산 어종을 철마다 선보이는 강릉시 주문진수산시장의 시장 활성화 사업의 일환으로 시장의 공간 조성에 필요한 일러스트레이션과 그래픽 작업을 진행했습니다. 시장의 부출입구로 사람들이 쉽게 입장할 수 있으면서 시장의 이야기를 담을 수 있도록 동해 바다에서 잡히는 어종을 묘사한 주문진 바다 벽화와 어촌의 정취가 담아 다양한 공연을 여는 시장 옥상 꽁치극장의 무대와 바닥 파도 그림을 그리고 바람이 불면 물고기 모양으로 펼쳐지는 바람물고기 조형물을 디자인했습니다.
+기획 진행 | 감자꽃 스튜디오, 갤러리팩토리
+꽁치극장 설계 | 조재원 [01스튜디오]
+그래픽 &amp; 일러스트레이션 | 한지인</t>
+  </si>
+  <si>
+    <t>주문진 바다 그림과 바람물고기
+주문진 수산시장</t>
+  </si>
+  <si>
+    <t>1910년부터 이어져 온 유서깊은 강릉시의 옥계시장의 시장 활성화 사업의 일환으로 시장과 축제에 필요한 그래픽 작업을 진행했습니다. 사업과 함께 만들어진 ‘오케이, 옥계’라는 슬로건을 바탕으로 아이덴티티를 만들고, ‘오케이 장터나들이’, ‘오케이옥계 추석맞이 한마당’, ‘농촌체험관광축제’, ‘옥계 마늘 축제’, ‘옥계 한마음 축제’ 등의 행사를 위한 각종 홍보물과 일러스트레이션을 제작했습니다.
+기획 | 감자꽃 스튜디오
+아이덴티티 디자인 | 공연지, 한지인
+그래픽 디자인 | 한지인
+일러스트레이션 | 한지인</t>
+  </si>
+  <si>
+    <t>옥계시장 브랜딩
+&lt;오케이, 옥계&gt; 활성화 사업</t>
+  </si>
+  <si>
+    <t>maker</t>
+  </si>
+  <si>
+    <t>editor</t>
+  </si>
+  <si>
+    <t>facillitator</t>
   </si>
 </sst>
 </file>
@@ -1042,9 +1173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1068,6 +1196,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1411,35 +1542,35 @@
     <col min="2" max="2" width="9.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="43.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="43.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.6640625" style="13" customWidth="1"/>
     <col min="7" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1454,13 +1585,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>194</v>
+      <c r="F2" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>22</v>
@@ -1483,12 +1614,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1506,12 +1637,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -1529,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E5" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>193</v>
+      <c r="F5" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>27</v>
@@ -1552,13 +1683,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E6" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>192</v>
+      <c r="F6" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>27</v>
@@ -1572,13 +1703,13 @@
         <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>191</v>
+      <c r="F7" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>27</v>
@@ -1592,12 +1723,12 @@
         <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>189</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -1615,13 +1746,13 @@
         <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>247</v>
+      <c r="F9" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>26</v>
@@ -1638,12 +1769,12 @@
         <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -1658,13 +1789,13 @@
         <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E11" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>190</v>
+      <c r="F11" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>37</v>
@@ -1681,19 +1812,19 @@
         <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>217</v>
       </c>
+      <c r="F12" s="12" t="s">
+        <v>218</v>
+      </c>
       <c r="G12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,19 +1835,19 @@
         <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F13" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>219</v>
       </c>
+      <c r="F13" s="12" t="s">
+        <v>220</v>
+      </c>
       <c r="G13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1727,13 +1858,13 @@
         <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F14" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>221</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>27</v>
@@ -1747,19 +1878,19 @@
         <v>58</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="F15" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>223</v>
       </c>
+      <c r="F15" s="12" t="s">
+        <v>224</v>
+      </c>
       <c r="G15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1770,13 +1901,13 @@
         <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="F16" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>225</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>27</v>
@@ -1790,16 +1921,19 @@
         <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F17" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>227</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1812,14 +1946,17 @@
       <c r="D18" s="2">
         <v>2009</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F18" s="13" t="s">
+      <c r="E18" s="12" t="s">
         <v>229</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1832,11 +1969,11 @@
       <c r="D19" s="2">
         <v>2007</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>230</v>
+      <c r="E19" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>27</v>
@@ -1853,15 +1990,18 @@
         <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E20" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>231</v>
-      </c>
       <c r="G20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1873,39 +2013,45 @@
         <v>64</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>234</v>
       </c>
+      <c r="F21" s="12" t="s">
+        <v>235</v>
+      </c>
       <c r="G21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>27</v>
+      <c r="I21" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="F22" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>215</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1916,18 +2062,15 @@
         <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F23" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>240</v>
       </c>
+      <c r="F23" s="12" t="s">
+        <v>241</v>
+      </c>
       <c r="G23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1939,13 +2082,13 @@
         <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F24" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>242</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>37</v>
@@ -1959,22 +2102,22 @@
         <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F25" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>244</v>
       </c>
+      <c r="F25" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="G25" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1985,13 +2128,13 @@
         <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F26" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>246</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>27</v>
@@ -2004,8 +2147,18 @@
       <c r="C27" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="D27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
@@ -2014,8 +2167,21 @@
       <c r="C28" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="D28" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
@@ -2024,8 +2190,21 @@
       <c r="C29" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
@@ -2034,8 +2213,18 @@
       <c r="C30" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="D30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
@@ -2044,8 +2233,21 @@
       <c r="C31" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
@@ -2054,178 +2256,224 @@
       <c r="C32" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D32" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D34" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" s="2">
         <v>2008</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
     </row>
     <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
@@ -2328,9 +2576,9 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="10"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="11"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="10"/>
     </row>
     <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
@@ -2682,9 +2930,9 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="11"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
     </row>
     <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
@@ -2772,13 +3020,13 @@
         <v>44</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F114" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E114" s="12" t="s">
         <v>213</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Library/Mobile Documents/com~apple~CloudDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B7AEF-BCC0-CD4E-B35F-14D8D1569855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFC8D09-81F0-B940-9711-1DF04E0A6098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="680" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="1960" yWindow="700" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="311">
   <si>
     <t>category</t>
   </si>
@@ -1085,6 +1085,182 @@
   </si>
   <si>
     <t>facillitator</t>
+  </si>
+  <si>
+    <t>2009,2010,2011</t>
+  </si>
+  <si>
+    <t>2007,2008,2009</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016,2017</t>
+  </si>
+  <si>
+    <t>2023,2024</t>
+  </si>
+  <si>
+    <t>2021,2022,2023</t>
+  </si>
+  <si>
+    <t>2022,2025</t>
+  </si>
+  <si>
+    <t>2023, 2024</t>
+  </si>
+  <si>
+    <t>2025,2026</t>
+  </si>
+  <si>
+    <t>국토해양부 국토환경디자인 공모사업의 일환으로 진행된 마을 만들기 사업에서 브랜딩으로 참여했습니다. 건축가, 조경가, 생태학자, 환경교육 전문가, 커뮤니티 계획가 등과 함께 조성하는 마을 사업이 그 누구보다 주민과 함께할 수 있는 방법을 고안하여 워크샵을 열어 그림을 그리고 만들기를 하고 밥을 먹으며 이야기를 나누었습니다. 워크샵에서 도출된 결과물은 마을 만들기에서 다양한 캐릭터로 활용되어 주민이 만든 디자인으로 선보였습니다.
+아트선재센터에서 있었던 양지리 철새마을 전시 소개
+http://www.lafent.com/news2/sub_01_view_print.html?news_id=106548&amp;b_cate=10&amp;m_cate=01
+PM | 한지인
+디자인 | 조기상, 이효섭, 이장섭, 홍민아</t>
+  </si>
+  <si>
+    <t>철새협동鳥합
+철원군 양지리 철새마을 브랜딩</t>
+  </si>
+  <si>
+    <t>신세계 푸드마켓의 리뉴얼 오픈 이후 활용할 수 있는 기프트 패키징 디자인에 대한 리서치와 전략 개발, 디자인, 샘플 제작에 걸친 작업을 진행했습니다. 기존의 과일바구니에서 벗어나는 새로운 시도를 하려는 신세계백화점 디자인팀과 좋은 협력 관계를 통해 시너지를 낼 수 있었던 도전적인 프로젝트였습니다.
+기획 진행 | 신세계백화점 디자인팀
+디자인 전략 | 김승연, 정다운, 한지인
+샘플 제작 | 김승연, 김세형, 김민선, 김아미, 이규원, 정다운, 한지인</t>
+  </si>
+  <si>
+    <t>신세계 기프트 패키징 디자인
+for renewed FOOD MARKET</t>
+  </si>
+  <si>
+    <t>갤러리팩토리와 도쿄 포일갤러리가 공동 기획한 일본 현대미술작가 5인의 전시 &lt; alive_birth of a tale&gt;전시를 위한 아이덴티티와 홍보물을 디자인했습니다. 기획자가 참 좋아해주신 디자인이라 기분이 좋았습니다.
+전시 소개
+http://factory483.org/exhibition/704
+진행 | 갤러리팩토리
+디자인 | 한지인
+ </t>
+  </si>
+  <si>
+    <t>alive_birth of a tale
+갤러리팩토리 X FOIL 국제교류전</t>
+  </si>
+  <si>
+    <t>동물학자들이 만든 제주의 카페 유인원 필드스테이션의 오픈에 맞춰 제주의 자연을 모티브로 하는 일러스트레이션을 개발하여 스카프, 피크닉 매트, 엽서, 공간 패브릭을 디자인 및 제작하였습니다. 더불어 추후 판매 예정인 ‘탐험가 굿즈’ 라인의 MD작업을 진행하였습니다.
+제주의 자연을 들여다보며 조심스럽게 그림을 그려가는 동안, 그렇게 자주 제주에 왔으면서도 아직 보지 못했던 구석구석 아름답고 놀라운 장면들이 있다는 사실에 마음이 설렜습니다. 더 많은 분들이 유인원이라는 팀을 통해 제주의 자연을 더 자세하게 마음 속에 들이시기를 바랍니다.
+유인원 계정
+https://www.instagram.com/uio.apes/
+유인원 필드스테이션 계정
+https://www.instagram.com/uio.fieldstation/
+기획, 진행 | 유인원 김예나, 안재하
+일러스트레이션, 디자인, 제작 | 한지인</t>
+  </si>
+  <si>
+    <t>유인원 uio
+제주의 자연을 닮은 굿즈</t>
+  </si>
+  <si>
+    <t>명륜동 작업실, 오래된 집 등의 전시장과 레지던시를 운영하고 다양한 문화예술 프로그램을 기획하는 사단법인 캔파운데이션의 리브랜딩 작업을 진행했습니다. 아이덴티티과 인쇄물, 각종 서식, 웹사이트 등 각종 어플리케이션을 디자인했습니다.
+캔파운데이션 공식사이트
+https://can-foundation.org
+진행 | 캔파운데이션
+디자인 | 한지인</t>
+  </si>
+  <si>
+    <t>캔 파운데이션
+예술창작 지원 비영리단체</t>
+  </si>
+  <si>
+    <t>마포에서 공중텃밭을 운영하는 도시청년농부 파절이(파릇한 절믄이)가 직접 키운 홉으로 만든 맥주를 선보이는 첫번째 팝업을 위한 그래픽 작업을 했습니다. 정말 맛있었습니다!
+파릇한절믄이 계정
+https://www.instagram.com/pajeori_urbanfarmer/
+진행 | 파릇한절믄이
+디자인 | 한지인
+협력 | 어메이징 브루잉 컴퍼니</t>
+  </si>
+  <si>
+    <t>파릇한 절믄이 로컬맥주파티
+직접 기른 홉으로 만든 진짜로컬맥주</t>
+  </si>
+  <si>
+    <t>생명다양성재단, 시셰퍼드코리아 등 동물권 단체가 공동 개최한 동물의 사육제 두번째, 쓰레기와 동물과 시에서 만들기팀으로 활동했습니다. 동물의 사육제 2019-쓰동시에서는 본 행사 이전에 ‘쓰레기 액츄얼리’ 캠페인을 진행하였으며, 만들기팀의 제작물은 캠페인부터 함께 했습니다. 쓰레기를 잔뜩 담고 있는 거북이들이 일회용품을 많이 사용하는 가게를 어택하거나 길거리에서 플래쉬몹을 하고 길거리 시위를 하는 등 동시다발적인 거북이의 행렬을 지원하고, 캠페인 영상에도 일부 출연했습니다.
+쓰동시 축제 현장에는 참가자들이 쓰레기로 만든 오브제를 하나씩 걸치고 입장할 수 있도록 쓰레기로 만든 오브제 다발을 만들어 제공했습니다.
+동물의 사육제 2019 쓰동시를 알리는 첫 포스트
+https://www.instagram.com/p/BzXndRcHrWs/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+만들기팀 | 서공희, 이규원, 한지인
+ </t>
+  </si>
+  <si>
+    <t>쓰동시
+동물의 사육제 2019 – 쓰레기와 동물과 시</t>
+  </si>
+  <si>
+    <t>생명다양성재단, 시셰퍼드코리아 등 동물권 단체가 공동 개최한 동물의 사육제 첫번째 해, 동물축제 반대축제에서 마스크 데스크 아트디렉터로 활동했습니다. 이 축제는 동물의 이름을 내세워 동물을 학대하는 기존 동물 축제에 문제를 제기하며 동물없는 동물축제에 사람들만을 초대해 참가하는 모두가 동물이 되어보는 경험을 제공하였습니다. 마스크 데스크에서는아티스트, 기획자에게 동물 분장 제작물(탈, 꼬리, 장갑 등)을 제공하고, 축제 현장에서 참가자들이 직접 자신을 위한 분장품을 만들 수 있도록 제작을 도와주는 역할을 수행했습니다.
+동물의 사육제 2018동축반축을 알리는 첫 포스트
+https://www.instagram.com/p/Bj7MzEUlfSa/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+마스크 데스크 팀 | 김성경, 서공희, 육다솔, 이규원, 정보석
+마스크 데스크 아트디렉터 | 한지인
+마스크 데스크 사전 제작물 | 낙지, 광어, 철새, 반딧불이, 산천어, 미꾸라지, 대하, 고래, 붕장어, 대게, 소, 나비</t>
+  </si>
+  <si>
+    <t>동축반축
+동물의 사육제 2018 - 동물축제 반대축제</t>
+  </si>
+  <si>
+    <t>동물학자들의 연구실에서 연구와 교육에 관한 활동을 지원하는 디자이너로 일했습니다. 각종 학회와 심포지엄, 공청회 등 학술 관련 행사의 아이덴티티와 포스터, 책자 등 인쇄물을 디자인하고 청소년과 어린이를 위한 교육 활동에 필요한 아이덴티티와 각종 그래픽과 인쇄물, 크고 작은 입체물, 스타일링 등 다양한 범위의 작업을 진행했습니다. roots and shoots(뿌리와 새싹), 습지외교관, 야외생물학자의 연구실, 엉터리 식물학자의 연구실, 다윈 해사, 봉서산 여름캠프, 통섭원 등의 활동을 함께 했습니다.</t>
+  </si>
+  <si>
+    <t>야외생물학자의 연구실 외
+이화여대 에코과학부 동물행동생태연구실</t>
+  </si>
+  <si>
+    <t>갤러리팩토리의 의뢰를 받아 제작한 두 마리의 부엉이 인형입니다. 이 중 하나의 부엉이는 팩토리옥션 2009년 12월 28일 가가린 &amp; 팩토리 옥션에 출품되어 경매에 낙찰되었습니다.
+의뢰 | 갤러리팩토리 홍보라
+디자인, 제작 | 한지인</t>
+  </si>
+  <si>
+    <t>부엉이
+commissioned works</t>
+  </si>
+  <si>
+    <t>‘이야기와 동물과 시’를 떠드는 창작집단 way 의 입체물 작업자로 활동했습니다. 동료 김한민의 책 ‘혜성을 닮은 방’을 모티브로 다른 작업자들과 함께 작업실 공간을 꽉 채워 두 차례 전시를 열었습니다. 이야기에 등장하는 다양한 캐릭터를 점토, 천, 펠트(양모로 직접 제작한 펠트!), 오래된 종이, 나무, 스타킹 등 다양한 재료로 제작하는 일을 전담했습니다. 전시 오프닝에 참석한 사람들을 위한 작고 괴상한 오브제 브로치를 작업해 나눴습니다.
+책 &lt;혜성을 닮은 방&gt;
+https://semicolon.minumsa.com/book/45/
+그림 | 김한민
+영상 | 김도형, 박세준
+입체물 제작 | 한지인</t>
+  </si>
+  <si>
+    <t>혜성을 닮은 방
+way studio</t>
+  </si>
+  <si>
+    <t>휠체어를 사용하는 사람들을 대상으로 장애인 화장실 현황을 실시간을 확인할 수 있는 지도 서비스를 위한 아이덴티티와 버벌 브랜딩 작업을 진행했습니다. 기술을 기반으로 소셜 임팩트를 만들어내는 스타트업 베이띵스는 무장애 여행을 지원하는 정보를 공유하여 누구나 즐거운 외출을 할 수 있는 사회적 기반을 만드는 기업입니다.
+대표님의 초심과 사업을 만들어가는 이야기를 인터뷰하며 창업가의 아이디어가 사회와 연결되는 순간을 목격할 수 있어 무척 설레었습니다. 베이띵스와 노크노크가 펼쳐갈 다음 챕터를 기대합니다.
+노크노크 계정
+https://www.instagram.com/knock.wiki/
+기획 인터뷰 버벌 브랜딩 | 이혜승, 한지인
+디자인 | 한지인</t>
+  </si>
+  <si>
+    <t>노크노크 브랜딩
+베이띵스가 만든 장애인 편의시설 지도 서비스</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2448,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>112</v>
       </c>
@@ -2295,7 +2471,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>113</v>
       </c>
@@ -2315,7 +2491,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>114</v>
       </c>
@@ -2335,127 +2511,265 @@
         <v>270</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D36" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D42" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D43" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-    </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D46" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D47" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>210</v>
       </c>
@@ -2464,6 +2778,9 @@
       </c>
       <c r="C48" s="3" t="s">
         <v>211</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2008</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -2485,6 +2802,9 @@
       <c r="C50" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="D50" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
@@ -2496,6 +2816,9 @@
       <c r="C51" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D51" s="3" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
@@ -2504,6 +2827,9 @@
       <c r="C52" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="D52" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -2512,6 +2838,9 @@
       <c r="C53" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="D53" s="3" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
@@ -2520,6 +2849,9 @@
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="D54" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -2529,6 +2861,9 @@
       <c r="C55" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="D55" s="3" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
@@ -2538,6 +2873,9 @@
       <c r="C56" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="D56" s="3" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
@@ -2547,6 +2885,9 @@
       <c r="C57" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="D57" s="3" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
@@ -2556,6 +2897,9 @@
       <c r="C58" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="D58" s="3" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
@@ -2565,6 +2909,9 @@
       <c r="C59" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="D59" s="3" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
@@ -2573,6 +2920,9 @@
       <c r="B60" s="4"/>
       <c r="C60" s="3" t="s">
         <v>55</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2590,6 +2940,9 @@
       <c r="C62" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="D62" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
@@ -2601,6 +2954,9 @@
       <c r="C63" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D63" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
@@ -2609,24 +2965,33 @@
       <c r="C64" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D64" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D65" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D66" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>142</v>
       </c>
@@ -2634,8 +2999,11 @@
       <c r="C67" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D67" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>143</v>
       </c>
@@ -2645,8 +3013,11 @@
       <c r="C68" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D68" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>144</v>
       </c>
@@ -2656,64 +3027,88 @@
       <c r="C69" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D69" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D70" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D71" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D72" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D73" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D74" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D75" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D76" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>152</v>
       </c>
@@ -2721,39 +3116,51 @@
         <v>44</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D78" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D79" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D80" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D81" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>157</v>
       </c>
@@ -2761,180 +3168,243 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D83" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D84" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D85" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D86" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D87" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D88" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D89" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D90" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D91" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D92" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D93" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D94" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D95" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D96" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D97" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D98" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D99" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D100" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D101" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D102" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D103" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
       <c r="C104" s="10"/>
     </row>
-    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>179</v>
       </c>
@@ -2944,8 +3414,11 @@
       <c r="C105" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D105" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>180</v>
       </c>
@@ -2955,53 +3428,74 @@
       <c r="C106" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D106" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D107" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D108" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D109" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D110" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D111" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3010,6 +3504,9 @@
       </c>
       <c r="C113" s="3" t="s">
         <v>43</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3041,7 +3538,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B72D82-9823-C241-8645-4BCD8A0E8126}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Library/Mobile Documents/com~apple~CloudDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFC8D09-81F0-B940-9711-1DF04E0A6098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D212470-DA1E-3F4B-B3DE-AA606A6CC3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1960" yWindow="700" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="338">
   <si>
     <t>category</t>
   </si>
@@ -1261,6 +1261,204 @@
   <si>
     <t>노크노크 브랜딩
 베이띵스가 만든 장애인 편의시설 지도 서비스</t>
+  </si>
+  <si>
+    <t>물건의 가치와 효용성에 대해 여러가지 생각과 실험, 제작이 돋보였던 디자인메이드 2008 ‘Saving by Design’ 전시의 전시디자인과 편집디자인으로 참여했습니다. 한국디자인문화재단에서 주최하고 예술의전당 디자인미술관에서 열린 디자인메이드 2008은 네덜란드 디자인재단 PLATFORM 21과 함께 ‘해킹 이케아 Hacking IKEA’ 섹션을, 스페인 신발 브랜드 ‘CAMPER’와는 폐기물과 신발 소재에 관한 섹션을 구성하는 등 국내외 파트너쉽을 통해 다양한 시도를 초대해 펼쳤습니다.
+전시 디자인과 도록 디자인 또한 전시에서 전하고자 하는 메세지를 충분히 담기 위한 노력이 동반되었습니다. 전시에 사용된 대부분의 재료는 수개월간 도처에서 수집한 폐기물을 재활용하여 디자인되었으며, 재폐기시 환경적 위해가 없을 것을 가장 우선시하여 제작 공정을 살폈습니다. 더불어, 전시폐기물을 활용한 Saving by Design Plus+ 전을 개최하여 후속 기획을 진행하기도 했습니다.
+기획총괄 | 김상규
+큐레이터 | 장인기, 이은경, 이혜림, 신단비
+아트디렉터 | 이장섭
+전시디자인 | 한지인
+편집 디자인 | 이장섭, 한지인
+시공 | 나무한그루
+테크니컬 매니저 | 곽종현</t>
+  </si>
+  <si>
+    <t>Saving by Design
+design made 2008</t>
+  </si>
+  <si>
+    <t>도넛 경제학을 현실에서 실천하는 글로벌 커뮤니티의 축제, 글로벌 도넛데이에 한국 커뮤니티인 도넛집의 멤버로 도넛데이의 진행을 함께했습니다. 동료들과 함께 글로벌 온라인 행사에 참가하고, 도넛집만의 행사인 워크샵과 포럼을 만들고 온오프라인 디자인을 진행했습니다. 도넛집 포럼에서는 ‘비즈니스 차원의 도넛’을 주제로 발표를 맡아 진행했습니다.
+도넛집의 2025 글로벌도넛데이 포스트
+https://www.instagram.com/p/DPxlsB7EfPw/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==
+도넛집의 2025 글로벌도넛데이 노션
+https://jongho1.notion.site/2025-X-26f1b72e06d480d99ca1ecf66e8f6142
+주최 | 도넛집 (이가람, 여미영, 원종호, 한지인, 한선경, 박혜연) 
+협력 | 씨닷, 녹색전환연구소, 임팩트얼라이언스</t>
+  </si>
+  <si>
+    <t>One Step Forward: Read to Move
+글로벌 도넛데이 2025 X 도넛집</t>
+  </si>
+  <si>
+    <t>요일마다 주인이 바뀌는 상수동 공간 ‘프로젝트 하다’에서 일요일 아침부터 점심까지 여는 식당을 운영했습니다.
+아침 계정
+https://www.instagram.com/aachime/</t>
+  </si>
+  <si>
+    <t>아침 aachime
+프로젝트 하다의 일요아침식당</t>
+  </si>
+  <si>
+    <t>행정안전부에서 발주하고 협동조합 청풍이 수행하는 청년마을 필드워크 캠프 사업에서 협력 운영하는 듣는연구소 협동조합의 퍼실리테이터로 일했습니다.
+지역으로 이주한 청년들이 자신들의 고민과 경험을 체계적으로 성찰하고 답을 찾아갈 수 있는 ‘성찰적 학습모임’을 액션리서치 (Action Research) 방식으로 접근, 기획한 연구 사업을 위한 두 차례의 캠프 중 공주(도약편)에서 진행을 원활하게 하는 퍼실리테이터로 현장의 이야기 속에서 새로운 앎을 건져올리기 위한 워크샵과 대화에 참여했습니다.
+많은 참가자들이 지역에 정착하여 자신의 삶과 지역에 변화를 만들어가기 위해 함께 이야기를 나누는 가운데에서 저 또한 제 삶을 돌아볼 수 있는 소중한 경험이었습니다.
+협동조합 청풍 뉴스레터에 등장한 캠프 (결과기록집 요청링크 있음)
+https://stibee.com/api/v1.0/emails/share/2L_8yQOHtXp2de5VGUNHORGECOKYQ0w
+연구 발주 | 행정안전부
+수행 | 협동조합 청풍
+협력 운영 | 듣는연구소 우성희, 백희원
+공주 캠프 퍼실리테이터 | 조윤정, 한지인</t>
+  </si>
+  <si>
+    <t>청년마을 필드워크 캠프 ‘공주’
+듣는연구소 협동조합 액션리서치</t>
+  </si>
+  <si>
+    <t>농부시장 마르쉐에 출점하는 농가 중 3개팀을 대상으로 하는 브랜딩 프로젝트에서 브랜딩 슈퍼바이저 역할으로 프로젝트를 운영했습니다. 새벽부터 밤늦게까지 농사와 가공, 판매를 위한 시간을 보내시는 작은 농가가 농부시장에 나와서 고객을 대할 때 필요한 상황을 고려하여 아이덴티티 작업을 기반으로 각 팀별로 필요한 VMD 작업을 진행하였습니다.
+기획 | 농부시장 마르쉐
+슈퍼바이저 | 한지인
+디자이너 | 강심지, 신영은, 지상이
+참여 농가 | 밤아저씨, 홍성자연재배 협동조합, 준혁이네</t>
+  </si>
+  <si>
+    <t>농가 브랜딩
+농부시장 마르쉐의 3개 농가 프로젝트</t>
+  </si>
+  <si>
+    <t>서울의 열가지 색과 연결되는 서울의 디자이너 10인의 디자인 전시를 기획하고 진행하는 일을 했습니다. 다양한 의견이 교차하는 자하 하디드의 DDP가 완성되고 진행되는 햇전시에서 새 공간의 낮과 밤을 오랫동안 함께하며 흥미로운 시간을 가질 수 있었습니다.
+서울디자인재단 자료
+https://seouldesign.or.kr/index.html?menuno=542&amp;cateno=162&amp;etc5=kor
+주최 | 서울특별시
+주관 | 서울디자인재단
+전시 감독 | 박진우
+전시 디자인 | 지엔피크리에이티브, 고가현
+전시 진행 | 갤러리팩토리, 한지인</t>
+  </si>
+  <si>
+    <t>10/10
+서울 10색과 10인의 디자이너전</t>
+  </si>
+  <si>
+    <t>중소벤처기업부와 소상공인시장진흥공단이 주관하는 글로컬 상권 창출 프로젝트로 선정된 어반플레이의 서촌 로컬 비즈니스 생태계 강화 프로그램 중 최종성과 축제인 &lt;에디션 서촌&gt;의 비쥬얼 아카이빙 작업을 진행하는 매니저로 일했습니다.
+전체 행사를 홍보하기 위한 영상의 기획과 진행을 함께하고, 행사 중 총 35개 스팟에서 진행되는 프로그램과 설치 조형물을 대상으로 비디오/포토 아카이빙을 진행했습니다.
+에디션서촌 계정
+https://www.instagram.com/editionseochon/
+주최 주관 | 중소벤처기업부, 소상공인시자진흥고단
+기획 운영 | 어반플레이
+비쥬얼 아카이빙 | 팀 도밍고(영상), 임효진(사진), 한지인(매니징)</t>
+  </si>
+  <si>
+    <t>에디션 서촌</t>
+  </si>
+  <si>
+    <t>“일상에서 누리는 널리 이로운 디자인, 길몸삶터”라는 주제로 열린 2022년 공공디자인 페스티벌에서 ‘길’ 섹션 &lt;두루두루 시장 Market for All&gt;의 협력 큐레이터로 일했습니다.
+&lt;두루두루 시장&gt;은 지속가능성, 접근성, 포용성 등의 가치를 상품과 서비스에 함께 녹여 시장에서 활발하게 활동하고 있는 총 28개 기업을 위한 시장입니다. 문화역284 3등 대합실을 배경으로 총 4주간 매주 달라지는 셀러로 구성된 시장 기획, 섭외, 진행, 운영 및 에디팅 업무를 맡아 진행했습니다.
+길몸삶터 계정
+https://www.instagram.com/designeverydaylife.kr/
+주최 | 문화체육관광부
+주관 | 한국공예디자인문화진흥원
+감독 | 안병학
+큐레이터 | 석재원, 김예니, 김한솔
+초대 큐레이터 | 김형재, 홍은주, 권준호, 김경철, 김어진, 김건태
+협력 큐레이터 | 이영주, 최홍주, 한지인, 박한별, 조혜연
+보조 큐레이터 | 문사라
+아이덴티티, 코디네이터 | 박용훈, 양효정
+시노그래피 | 김병국, 민경문</t>
+  </si>
+  <si>
+    <t>두루두루 시장
+2022 공공디자인 페스티벌</t>
+  </si>
+  <si>
+    <t>서울시를 비롯한 전국 각 지역의 로컬크리에이터가 배출되는 가운데, 서초구에서 자체적으로 행정구역내에서 로컬크리에이터를 선정하는 사업의 운영을 맡아 진행했습니다. 
+전국단위 홍보를 통해 총 6팀을 심사, 선발하는 과정부터 온오프라인 강의 교육, 커뮤니티 피어러닝, 로컬 창업가와의 만남 등의 프로그램을 진행하고 최종 성과 공유회로 마무리하는 여정을 통해 참가팀의 33%가 구역내에서 창업하는 좋은 성과를 내기도 했습니다. 
+로컬인서울 양재 계정
+https://www.instagram.com/localinseoul.yj/
+주최 | 서초구청 밝은미래국 일자리경제과
+주관 | 서초여성일자리주식회사
+운영 | 한지인 [오알비]
+커뮤니티 매니저 | 변지현
+컨텐츠 에디터 | 변지현
+멘토단 | 김시내, 문석진, 우영승, 이혜미, 최용경
+스탭 | 권지희</t>
+  </si>
+  <si>
+    <t>로컬인서울, 양재
+양재천길상권 로컬크리에이터 양성용역</t>
+  </si>
+  <si>
+    <t>서울시 로컬브랜드 육성사업의 첫 해인 2022년, 총 5개 상권 중 4개 상권 8개 사업체를 대상으로 진행한 브랜딩 액션캠프의 총괄 코치로 활동했습니다. 총 5주간 1:1 밀착형 현장 대면 코칭과 온라인 피어러닝을 통해 직접적인 컨설팅을 진행, 버벌 브랜딩과 비쥬얼 브랜딩 요소를 추출하고, 마케팅/디자인 전문가와 함께 최종 산출물을 만들어 실제 사용가능한 결과물을 만들어내는 액션플래닝의 실행했습니다. 사업 최종 발표회는 팝업 마켓의 형태로 기획되어 8개 팀이 한 자리에서 자신의 브랜드를 홍보 및 제품을 판매되었으며 성황리에 마무리되었습니다.
+또한, 본 사업의 취지인 “서울 안에 있는 각각의 동네가 모두 서울의 로컬, 서울의 다양한 동네를 흥미롭게 들여다 보고 좋은 가게들을 응원하자’는 마음을 담아 ‘동네서울’이라는 네이밍 개발을 진행하였습니다.
+동네서울 코칭 아카이브 by 언더독스
+#동네서울 에필로그
+https://www.youtube.com/watch?v=1SRW4WmwcAM
+#1 리뉴얼
+https://youtu.be/3TKYwS-qJFc?si=ncGGlN2g-nbkBiO3
+#2 버벌브랜딩
+https://www.youtube.com/watch?v=SLpwCUx0nGQ
+#3 세일즈 마케팅 전략
+https://www.youtube.com/watch?v=cDr5jQdF4o8
+#4 비쥬얼 브랜딩
+https://www.youtube.com/watch?v=2yIeH7z-pLs
+#5 로컬브랜딩과 액션플래닝
+https://www.youtube.com/watch?v=ISFYBD0pOk8
+동네서울 브랜드 마켓 현장 스케치
+https://www.youtube.com/watch?v=xy_6LbNreco
+주최 | 서울특별시 
+주관 | 서울신용보증재단
+운영 | 언더독스
+총괄 코치 | 한지인
+코칭 스탭 | 주하나
+액션플래너 | 이소현, 이연성, 이혜승, 홍민아</t>
+  </si>
+  <si>
+    <t>동네서울
+2022 서울 로컬브랜드 상권조성 프로젝트</t>
+  </si>
+  <si>
+    <t>2022년을 시작으로 2024년까지 총 3년간 선정된 서울시내 총 9개 로컬브랜드 상권의 총 30개 사업체를 대상으로 ‘브랜딩 액션러닝’ 트랙을, 2024년 신규 선정된 2개 로컬브랜드 상권에서 창업을 원하는 총 11개팀을 대상으로 ‘로컬인서울’ 트랙을 운영하는 사업에서 브랜딩 액션러닝 코칭 총괄과 브랜딩 액션러닝/로컬인서울 SNS운영/핸드북 제작 업무를 진행했습니다.
+브랜딩 경험이 풍부한 10명의 코치와 2명의 강사를 초빙하여 총 4개월간의 여정을 함께하며 서울 곳곳의 열정적인 사장님들의 성장을 돕는 일을 했습니다.
+2024 브랜딩 액션러닝 계정
+https://www.instagram.com/branding.action.learning/
+주최 | 서울특별시 
+주관 | 서울신용보증재단
+운영 | 언더독스
+코칭 디렉터 | 한지인
+코치 | 고다희, 김나영, 박유진, 박진실, 설미소, 신수하, 이재연, 이혜승, 하승우, 홍민아
+강사 | 정다운[보틀팩토리], 최용경[스몰브랜더]
+컨텐츠 에디터 | 권재윤, 김희영, 변지현
+핸드북 디자인 | 프론트킷</t>
+  </si>
+  <si>
+    <t>브랜딩 액션러닝 코칭
++로컬인서울 운영 지원
+2024 서울 로컬브랜드 상권조성 프로젝트</t>
+  </si>
+  <si>
+    <t>소상공인 역량 강화를 위해 서초구에서 추진하는 ‘골목상권 미식브랜딩’ 사업의 첫번째 운영을 맡아 진행했습니다. 동네 가게의 매력을 계속해서 발굴해 ‘작고 강한 로컬 브랜드’를 만들기 위한 서초형 미식 프로젝트의 일환으로 추진되었으며, F&amp;B 전문가와 브랜딩 전문가가 함께 팀을 이루어 레서피를 새로 개발하거나 기존 레서피를 개선하고, 팝업 행사 ‘델리살롱’을 통해 대중에게 선보이는 등의 액션플랜을 실행하였습니다. 팝업 행사인 ‘델리살롱’은 “우리동네 델리샵”을 컨셉으로, 골목 미식 가게의 새로운 레시피를 한시적으로 직접 구매할 수 있는 마켓입니다.
+매일 바삐 움직이시는 사장님들이 브레이크타임을 쪼개 컨설팅과 팝업 행사를 함께 해주시는 마음에 한 수 더 배울 수 있는 시간이었습니다. 
+델리살롱 지역뉴스 취재 영상
+https://www.youtube.com/watch?v=VcuM6rouCoY
+주최 | 서초구청 밝은미래국 일자리경제과 골목상권활성화팀
+주관 | 서초여성일자리주식회사
+운영 | 한지인 [오알비]
+F&amp;B 컨설팅 | 이현승, 하연선
+F&amp;B 모니터링 외 | 백석예술대학교 호텔조리 제과제빵학부 (고윤서, 김태호, 양지원, 이태윤, 장채원, 피은서, 박수찬)
+참여 가게 | 백가네, 서퍼스 포케, 시골집 청국장, 아인글라스, 청계산커피</t>
+  </si>
+  <si>
+    <t>델리살롱 Deli Salon
+서초구 골목상권 미식브랜딩 컨설팅</t>
+  </si>
+  <si>
+    <t>consultant</t>
+  </si>
+  <si>
+    <t>chef</t>
+  </si>
+  <si>
+    <t>crew</t>
   </si>
 </sst>
 </file>
@@ -2773,26 +2971,30 @@
       <c r="A48" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B48" s="2">
-        <v>2008</v>
-      </c>
       <c r="C48" s="3" t="s">
         <v>211</v>
       </c>
       <c r="D48" s="2">
         <v>2008</v>
       </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E48" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="10"/>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
     </row>
-    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>127</v>
       </c>
@@ -2805,8 +3007,23 @@
       <c r="D50" s="3" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>128</v>
       </c>
@@ -2819,8 +3036,20 @@
       <c r="D51" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>129</v>
       </c>
@@ -2830,8 +3059,17 @@
       <c r="D52" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>130</v>
       </c>
@@ -2841,8 +3079,23 @@
       <c r="D53" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>131</v>
       </c>
@@ -2852,8 +3105,17 @@
       <c r="D54" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>132</v>
       </c>
@@ -2864,8 +3126,17 @@
       <c r="D55" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>1010</v>
       </c>
@@ -2876,8 +3147,17 @@
       <c r="D56" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E56" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>133</v>
       </c>
@@ -2888,8 +3168,17 @@
       <c r="D57" s="3" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E57" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>134</v>
       </c>
@@ -2900,8 +3189,17 @@
       <c r="D58" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E58" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>135</v>
       </c>
@@ -2912,8 +3210,17 @@
       <c r="D59" s="3" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>136</v>
       </c>
@@ -2924,13 +3231,25 @@
       <c r="D60" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E60" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9"/>
       <c r="B61" s="11"/>
       <c r="C61" s="10"/>
     </row>
-    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>137</v>
       </c>
@@ -2944,7 +3263,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>138</v>
       </c>
@@ -2958,7 +3277,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>139</v>
       </c>

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Library/Mobile Documents/com~apple~CloudDocs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D212470-DA1E-3F4B-B3DE-AA606A6CC3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463A4B8C-089D-1143-9DA0-1A28C2B1D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="700" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="1960" yWindow="680" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="340">
   <si>
     <t>category</t>
   </si>
@@ -1459,6 +1459,18 @@
   </si>
   <si>
     <t>crew</t>
+  </si>
+  <si>
+    <t>클라이언트와 어떤 협업을 하는가가 프로젝트에 꽤 큰 영향을 미치는 브랜딩이라고 하는 일. 그동안 만났던 수많은 클라이언트와 프로젝트 중에서 좀 더 길게 공유하고 싶은 네 개의 일을 조명하는 글을 썼습니다. 그리고 마지막 챕터에서는 번아웃을 경험하고 떠났던 새로운 세계에서 다시 내 일로 돌아오게 되었던 경험에 대해 적었습니다.
+손을 잡는 브랜딩 교보문고 페이지
+https://product.kyobobook.co.kr/detail/S000001790440
+출판사 | 한겨레 출판사
+편집자 | 김단희
+디자인 | 워크스</t>
+  </si>
+  <si>
+    <t>손을 잡는 브랜딩
+단행본</t>
   </si>
 </sst>
 </file>
@@ -3262,6 +3274,12 @@
       <c r="D62" s="3" t="s">
         <v>206</v>
       </c>
+      <c r="E62" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
@@ -3857,7 +3875,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B72D82-9823-C241-8645-4BCD8A0E8126}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463A4B8C-089D-1143-9DA0-1A28C2B1D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5BA44-820F-134F-A6B6-9AE9146F28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="680" windowWidth="21460" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="6560" yWindow="680" windowWidth="27140" windowHeight="19660" activeTab="1" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
-    <sheet name="about" sheetId="2" r:id="rId2"/>
+    <sheet name="card_list view" sheetId="3" r:id="rId2"/>
+    <sheet name="about" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="451">
   <si>
     <t>category</t>
   </si>
@@ -497,114 +498,12 @@
     <t>지큐</t>
   </si>
   <si>
-    <t>온라인 클래스</t>
-  </si>
-  <si>
-    <t>상상캠퍼스</t>
-  </si>
-  <si>
-    <t>춘천관광</t>
-  </si>
-  <si>
-    <t>선화예고</t>
-  </si>
-  <si>
-    <t>울산</t>
-  </si>
-  <si>
-    <t>WBC</t>
-  </si>
-  <si>
-    <t>서울예대</t>
-  </si>
-  <si>
-    <t>집중실험실</t>
-  </si>
-  <si>
-    <t>스토리스튜디오</t>
-  </si>
-  <si>
-    <t>고려대</t>
-  </si>
-  <si>
-    <t>전주센터</t>
-  </si>
-  <si>
     <t>비마이비</t>
   </si>
   <si>
-    <t>에딧시티</t>
-  </si>
-  <si>
-    <t>곡성특강</t>
-  </si>
-  <si>
-    <t>북토크</t>
-  </si>
-  <si>
     <t>뉴그라운드</t>
   </si>
   <si>
-    <t>서초도서관</t>
-  </si>
-  <si>
-    <t>고대크리켓</t>
-  </si>
-  <si>
-    <t>넥젠</t>
-  </si>
-  <si>
-    <t>질문의진화</t>
-  </si>
-  <si>
-    <t>서디창업센터</t>
-  </si>
-  <si>
-    <t>리부트</t>
-  </si>
-  <si>
-    <t>오풍카라</t>
-  </si>
-  <si>
-    <t>청양맛포럼</t>
-  </si>
-  <si>
-    <t>ㅂㅔ러로컬</t>
-  </si>
-  <si>
-    <t>골목창업학교</t>
-  </si>
-  <si>
-    <t>신보특강</t>
-  </si>
-  <si>
-    <t>지브인</t>
-  </si>
-  <si>
-    <t>헤그스킬업</t>
-  </si>
-  <si>
-    <t>유한양행</t>
-  </si>
-  <si>
-    <t>언독GS</t>
-  </si>
-  <si>
-    <t>강화유유</t>
-  </si>
-  <si>
-    <t>여성민우회</t>
-  </si>
-  <si>
-    <t>컨셉진</t>
-  </si>
-  <si>
-    <t>뉴웨이즈</t>
-  </si>
-  <si>
-    <t>브랜드액티비즘</t>
-  </si>
-  <si>
     <t>넥스트로컬</t>
   </si>
   <si>
@@ -612,24 +511,6 @@
   </si>
   <si>
     <t>한국의서원</t>
-  </si>
-  <si>
-    <t>헤이그라운드</t>
-  </si>
-  <si>
-    <t>아르떼</t>
-  </si>
-  <si>
-    <t>언독드림위드</t>
-  </si>
-  <si>
-    <t>환경연합오풍</t>
-  </si>
-  <si>
-    <t>고민상담소</t>
-  </si>
-  <si>
-    <t>남양주</t>
   </si>
   <si>
     <t>오늘전통
@@ -764,10 +645,6 @@
     <t>관광두레 브랜딩 멘토</t>
   </si>
   <si>
-    <t>지역 주민 사업체를 지원하는 관광두레 (문화체육관광부 · 한국관광공사의 민관 협력 정책 사업)의 브랜딩 멘토로 2015년부터 2022년까지 활동했습니다. 봉화, 동해, 춘천, 연천, 곡성, 남해의 주민사업체의 컨설팅 업무를 진행하고 전국대회 강연, 서촌 마켓 &amp; 살롱 디자인 등의 작업을 수행했습니다.
-작지만 큰 우리나라의 구석구석을 찾아 자신만의 제품과 컨텐츠로 사업을 만들어가는 분들과 만나 맛있는 것도 정말 많이 먹고, 재미있는 이야기도 정말 많이 들었습니다. 지역에서 일을 일궈낸다는 것은 굉장한 자존감이고 자랑거리입니다.</t>
-  </si>
-  <si>
     <t>갈다 사이언스 미디어 페스티벌 2025
 삼청 사이언스 구락부</t>
   </si>
@@ -1112,21 +989,6 @@
   </si>
   <si>
     <t>2016,2017</t>
-  </si>
-  <si>
-    <t>2023,2024</t>
-  </si>
-  <si>
-    <t>2021,2022,2023</t>
-  </si>
-  <si>
-    <t>2022,2025</t>
-  </si>
-  <si>
-    <t>2023, 2024</t>
-  </si>
-  <si>
-    <t>2025,2026</t>
   </si>
   <si>
     <t>국토해양부 국토환경디자인 공모사업의 일환으로 진행된 마을 만들기 사업에서 브랜딩으로 참여했습니다. 건축가, 조경가, 생태학자, 환경교육 전문가, 커뮤니티 계획가 등과 함께 조성하는 마을 사업이 그 누구보다 주민과 함께할 수 있는 방법을 고안하여 워크샵을 열어 그림을 그리고 만들기를 하고 밥을 먹으며 이야기를 나누었습니다. 워크샵에서 도출된 결과물은 마을 만들기에서 다양한 캐릭터로 활용되어 주민이 만든 디자인으로 선보였습니다.
@@ -1461,23 +1323,505 @@
     <t>crew</t>
   </si>
   <si>
-    <t>클라이언트와 어떤 협업을 하는가가 프로젝트에 꽤 큰 영향을 미치는 브랜딩이라고 하는 일. 그동안 만났던 수많은 클라이언트와 프로젝트 중에서 좀 더 길게 공유하고 싶은 네 개의 일을 조명하는 글을 썼습니다. 그리고 마지막 챕터에서는 번아웃을 경험하고 떠났던 새로운 세계에서 다시 내 일로 돌아오게 되었던 경험에 대해 적었습니다.
-손을 잡는 브랜딩 교보문고 페이지
-https://product.kyobobook.co.kr/detail/S000001790440
-출판사 | 한겨레 출판사
-편집자 | 김단희
-디자인 | 워크스</t>
-  </si>
-  <si>
-    <t>손을 잡는 브랜딩
-단행본</t>
+    <t>손을 잡는 브랜딩</t>
+  </si>
+  <si>
+    <t>ESG 브랜딩 워크북</t>
+  </si>
+  <si>
+    <t>작은 브랜드가 살아가는 법</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>한겨레출판사</t>
+  </si>
+  <si>
+    <t>북스톤</t>
+  </si>
+  <si>
+    <t>찌판사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한국국제교류재단 </t>
+  </si>
+  <si>
+    <t>https://www.koreana.or.kr/koreana/an/arn/selectArNttInfo.do?bbsId=1109&amp;nttSn=120484</t>
+  </si>
+  <si>
+    <t>매우 당연한 시장, 마르쉐 / Farmers Markets Sow Connections</t>
+  </si>
+  <si>
+    <t>https://magazine.cheil.com/53115</t>
+  </si>
+  <si>
+    <t>제일기획 매거진</t>
+  </si>
+  <si>
+    <t>ESG 브랜딩은 어떻게 시작할 수 있을까?</t>
+  </si>
+  <si>
+    <t>브랜딩에 헛짓은 없다</t>
+  </si>
+  <si>
+    <t>GQ</t>
+  </si>
+  <si>
+    <t>https://www.gqkorea.co.kr/2024/03/13/모든-사업이-브랜드가-되지는-않는다/</t>
+  </si>
+  <si>
+    <t>요즘힙 요즘브랜드</t>
+  </si>
+  <si>
+    <t>모든 사업이 브랜드가 되지는 않는다</t>
+  </si>
+  <si>
+    <t>https://www.gqkorea.co.kr/2023/12/05/잘나가는-브랜드는-왜-줄을-서게-할까/</t>
+  </si>
+  <si>
+    <t>잘나가는 브랜드는 왜 줄을 서게 할까</t>
+  </si>
+  <si>
+    <t>요정 동료</t>
+  </si>
+  <si>
+    <t>FDSC.txt Vol.2: 생산과 멈춤</t>
+  </si>
+  <si>
+    <t>https://fdsc.kr/400</t>
+  </si>
+  <si>
+    <t>https://stonebc.com/archives/13229</t>
+  </si>
+  <si>
+    <t>무한루프의 브랜드 진화를 위해 'CX'</t>
+  </si>
+  <si>
+    <t>스톤브랜드컨설팅</t>
+  </si>
+  <si>
+    <t>브랜딩으로 불황 뛰어넘기</t>
+  </si>
+  <si>
+    <t>https://stonebc.com/archives/10789</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>https://product.kyobobook.co.kr/detail/S000214409291</t>
+  </si>
+  <si>
+    <t>https://product.kyobobook.co.kr/detail/S000061353875</t>
+  </si>
+  <si>
+    <t>https://product.kyobobook.co.kr/detail/S000001790440</t>
+  </si>
+  <si>
+    <t>야나두 클래스</t>
+  </si>
+  <si>
+    <t>15개의 프로젝트 사례로 완성하는 브랜딩 초격차 패키지</t>
+  </si>
+  <si>
+    <t>패스트캠퍼스</t>
+  </si>
+  <si>
+    <t>MKYU X 연세대학교 ESG 인플루언서 자격증 과정</t>
+  </si>
+  <si>
+    <t>MKYU</t>
+  </si>
+  <si>
+    <t>2025 집중실험실</t>
+  </si>
+  <si>
+    <t>MKYU 그린플루언서 자격증 과정</t>
+  </si>
+  <si>
+    <t>서울시공익활동지원센터</t>
+  </si>
+  <si>
+    <t>서울예술대학교 시각디자인전공</t>
+  </si>
+  <si>
+    <t>브랜드 디자인</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MUSuG1SeD2Q</t>
+  </si>
+  <si>
+    <t>16년차 브랜드 기획자가 말하는 ‘브랜딩’</t>
+  </si>
+  <si>
+    <t>이찌라 (구.책읽찌라)</t>
+  </si>
+  <si>
+    <t>스토리스튜디오 / 스페이스 이도</t>
+  </si>
+  <si>
+    <t>디자이너 특강 '공생'</t>
+  </si>
+  <si>
+    <t>고려대학교 교양교육원</t>
+  </si>
+  <si>
+    <t>2022 전주시 사회혁신활동주체 브랜딩 역량강화교육</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/CgTEC_RFBnC/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>전주시 사회혁신센터</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Cfq-SvDpL2q/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>상상플래닛</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/tzIOTa7UrNQ?si=XKEUOOR-MP_PI5_c</t>
+  </si>
+  <si>
+    <t>에딧시티프로젝트</t>
+  </si>
+  <si>
+    <t>https://tnnews.co.kr/archives/112977</t>
+  </si>
+  <si>
+    <t>2022 로컬크리에이터 역량강화교육</t>
+  </si>
+  <si>
+    <t>전남관광두레 지역협력센터</t>
+  </si>
+  <si>
+    <t>지속가능한 성장을 위한 ESG 사용법</t>
+  </si>
+  <si>
+    <t>엠프티폴더스</t>
+  </si>
+  <si>
+    <t>브랜드 기획자와의 작업 | 부캐로 다양한 나 찾기</t>
+  </si>
+  <si>
+    <t>디자이너 특강 '앞으로의 브랜딩 | 어제로부터 이어보기'</t>
+  </si>
+  <si>
+    <t>5! 브랜드 책방 in 성수 북토크 세션 | ESG 브랜딩 워크북</t>
+  </si>
+  <si>
+    <t>재단법인 서초문화재단</t>
+  </si>
+  <si>
+    <t>책 소개 바로가기</t>
+  </si>
+  <si>
+    <t>원문 링크</t>
+  </si>
+  <si>
+    <t>영상 보기</t>
+  </si>
+  <si>
+    <t>관련 기사 보기</t>
+  </si>
+  <si>
+    <t>브랜딩이 하는 일</t>
+  </si>
+  <si>
+    <t>고려대학교 브랜드 컨설팅학회 CREAKET</t>
+  </si>
+  <si>
+    <t>넥스트젠 코리아</t>
+  </si>
+  <si>
+    <t>서울문화재단</t>
+  </si>
+  <si>
+    <t>강원창조경제혁신센터, 강원관광재단</t>
+  </si>
+  <si>
+    <t>관련 내용 보기</t>
+  </si>
+  <si>
+    <t>https://www.sfac.or.kr/opensquare/notice/notice_list.do?bcIdx=115424</t>
+  </si>
+  <si>
+    <t>선화예술고등학교 미술부 디자인과</t>
+  </si>
+  <si>
+    <t>&lt;리부트캠프 Re:Boot Camp&gt; 고객 이해 기반 브랜딩</t>
+  </si>
+  <si>
+    <t>루트임팩트 이니셔티브팀</t>
+  </si>
+  <si>
+    <t>https://rootimpact.org/business/rebootcamp/</t>
+  </si>
+  <si>
+    <t>관련 사업 보기</t>
+  </si>
+  <si>
+    <t>서울디자인창업센터</t>
+  </si>
+  <si>
+    <t>더테이스트포럼 | 지속가능한 맛 브랜딩</t>
+  </si>
+  <si>
+    <t>더테이스트 청양</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Cj4s8COv5Mm/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>홍보 컨텐츠 보기</t>
+  </si>
+  <si>
+    <t>경기문화재단</t>
+  </si>
+  <si>
+    <t>https://youtu.be/B3Stnnh_nvM?si=BRzqZqr-_xp_bjc7</t>
+  </si>
+  <si>
+    <t>강연 영상 보기</t>
+  </si>
+  <si>
+    <t>홍보 영상 보기</t>
+  </si>
+  <si>
+    <t>서울신용보증재단</t>
+  </si>
+  <si>
+    <t>고창 100년학교 공간브랜딩 프로젝트 | BRANDED 공간</t>
+  </si>
+  <si>
+    <t>고창문화도시센터</t>
+  </si>
+  <si>
+    <t>좋은 브랜드가 뭘까?</t>
+  </si>
+  <si>
+    <t>GBIN 지브인</t>
+  </si>
+  <si>
+    <t>브랜드, 브랜딩, 프로세스, 기준</t>
+  </si>
+  <si>
+    <t>울산동구워케이션센터 온앤오프</t>
+  </si>
+  <si>
+    <t>WBC 반상회 | 나의 때려치움 연대기</t>
+  </si>
+  <si>
+    <t>유한양행 | ESG의 본질을 담은 마케팅</t>
+  </si>
+  <si>
+    <t>우먼스베이스캠프</t>
+  </si>
+  <si>
+    <t>유한양행 ESG 경영실</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DPvN44zCed9/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>유유기지 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">루트임팩트  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DQssDtSknLD/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>스몰브랜드 첫 걸음 | 나만의 브랜드 설계하기</t>
+  </si>
+  <si>
+    <t>넷플연가</t>
+  </si>
+  <si>
+    <t>함께일하는재단, GS리테일, 언더독스</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>서울공익활동지원센터</t>
+  </si>
+  <si>
+    <t>언더독스</t>
+  </si>
+  <si>
+    <t>[모두가 아는 브랜드를 키운 비법] 
+예비 CEO를 위한 실전 창업 브랜딩</t>
+  </si>
+  <si>
+    <t>지속가능한 브랜드를 꿈꾸며 | 
+ESG로 시작하는 좋은 브랜드 만들기</t>
+  </si>
+  <si>
+    <t>퇴근 후 브레인스토밍 한잔 | 
+ESG 브랜딩 워크북 라운드테이블</t>
+  </si>
+  <si>
+    <t>생태마을 디자인교육 EDE 경제적 차원 특강 | 
+지구 전환기 비즈니스 둘러보기</t>
+  </si>
+  <si>
+    <t>강원투어리즘스쿨 | 
+지속가능한 브랜드공간을 ESG로 연결하는 방법</t>
+  </si>
+  <si>
+    <t>서울예술교육 아카데미 &lt;질문의 진화&gt; 감각 확장 워크숍 | 
+관계성의 탐색 "손을 잡는 나와 나"</t>
+  </si>
+  <si>
+    <t>선화예고 전문가 초청 및 경쟁PT | 어떤 브랜딩을 어떻게</t>
+  </si>
+  <si>
+    <t>서울디자인창업센터 세미나&amp;워크숍 | 
+지속가능한 브랜딩 전략과 도구</t>
+  </si>
+  <si>
+    <t>서울시 디자인 스타트업 데모데이 | 
+디자이너가 만드는 지속가능한 브랜딩</t>
+  </si>
+  <si>
+    <t>2023 경기 디자인 페스타 베러 로컬(Better Local) | 
+ESG로 시작하는 좋은 로컬 브랜드 만들기</t>
+  </si>
+  <si>
+    <t>골목창업학교 공개특강 &lt;사장님의 체크 리스트&gt; | 
+우리 가게 브랜딩 워크숍</t>
+  </si>
+  <si>
+    <t>온앤오프데이 | 브랜딩을 말하다 : 
+브랜드의 본질부터 콘텐츠까지</t>
+  </si>
+  <si>
+    <t>청년농부 자립기반 특강 | 
+내 브랜드에 가장 적합한 브랜딩은 무엇일까?</t>
+  </si>
+  <si>
+    <t>헤이그라운드 스킬업 | 
+우리 조직에 딱 맞는 브랜딩 우선순위 정하기</t>
+  </si>
+  <si>
+    <t>GS리테일 에코소셜임팩트 프로젝트 | 
+대형 리테일 특화 브랜딩</t>
+  </si>
+  <si>
+    <t>서초구립도서관 직원역량강화교육 | 
+서초구 도서관 브랜딩 전략 및 개발</t>
+  </si>
+  <si>
+    <t>소셜 콜라보레이터 커뮤니티 | 
+사회적경제 조직을 위한 브랜딩</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>관광벤처기업 전문 컨설팅</t>
+  </si>
+  <si>
+    <t>okus</t>
+  </si>
+  <si>
+    <t>창의적 먹거리경제조직 발굴 및 지원_3대가 협동조합 / 여성협동조합노둣돌</t>
+  </si>
+  <si>
+    <t>한국의 서원 시행계획 수립 전략</t>
+  </si>
+  <si>
+    <t>헤이그라운드 브랜드파트</t>
+  </si>
+  <si>
+    <t>헤이그라운드 브랜딩 전략</t>
+  </si>
+  <si>
+    <t>드림위드 BEGIN AGAIN 멘토링 | 디아앤코</t>
+  </si>
+  <si>
+    <t>한국문화예술교육진흥원 아르떼 아카데미</t>
+  </si>
+  <si>
+    <t>CoP &lt;다시 만난 체계&gt; 사업 방향 설정을 위한 브랜드 컨설팅</t>
+  </si>
+  <si>
+    <t>2023-24</t>
+  </si>
+  <si>
+    <t>헤이그라운드 비영리 멤버쉽</t>
+  </si>
+  <si>
+    <t>헤이그라운드 비영리조직 성장지원 파트너</t>
+  </si>
+  <si>
+    <t>헤이그라운드 비영리 멤버쉽 | 
+&lt;우리 조직에 맞는 브랜드 만들고 키우기&gt;</t>
+  </si>
+  <si>
+    <t>루트임팩트 성장지원팀</t>
+  </si>
+  <si>
+    <t>루트임팩트 임팩트 캠퍼스</t>
+  </si>
+  <si>
+    <t>루트임팩트 임팩트 캠퍼스 리브랜딩</t>
+  </si>
+  <si>
+    <t>임팩트 프랜차이즈 브랜딩 멘토링 | 알키 / 와로</t>
+  </si>
+  <si>
+    <t>서울환경연합 브랜딩 전략</t>
+  </si>
+  <si>
+    <t>서울환경연합, 오늘의풍경</t>
+  </si>
+  <si>
+    <t>https://seoulpa.kr/home/kor/M734735249/center/business/view.do?idx=cb00d1a0008a85e71a41b8741facbffef2b2c652ae6690a2b4512a50e91d7b85&amp;eSearchValue1=&amp;searchValue2=&amp;searchValue3=0&amp;searchKeyword=상담소&amp;searchValue10=B&amp;pageIndex=1</t>
+  </si>
+  <si>
+    <t>2025 참가자 후기</t>
+  </si>
+  <si>
+    <t>공익활동 수요상담소 | 전문가 1:1 컨설팅 홍보분야</t>
+  </si>
+  <si>
+    <t>남양주상권 활성화 패키지 상인회 컨설팅</t>
+  </si>
+  <si>
+    <t>프론트킷</t>
+  </si>
+  <si>
+    <t>넥스트로컬 홈커밍데이 2025 전문가 컨설팅</t>
+  </si>
+  <si>
+    <t>경기도 사회적경제원</t>
+  </si>
+  <si>
+    <t>서울신용보증재단, 언더독스</t>
+  </si>
+  <si>
+    <t>2024 서울 로컬브랜드 상권조성 프로젝트 브랜딩 액션러닝 코칭 디렉터</t>
+  </si>
+  <si>
+    <t>2022 서울 로컬브랜드 상권조성 프로젝트 브랜딩 액션러닝 코치</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1509,6 +1853,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1547,7 +1899,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1577,14 +1929,35 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1921,15 +2294,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="43.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.6640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="43.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.6640625" style="12" customWidth="1"/>
     <col min="7" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -1942,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>16</v>
@@ -1971,13 +2344,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>195</v>
+      <c r="F2" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>22</v>
@@ -2000,12 +2373,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -2023,12 +2396,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -2046,13 +2419,13 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E5" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>194</v>
+      <c r="F5" s="11" t="s">
+        <v>154</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>27</v>
@@ -2069,13 +2442,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>193</v>
+      <c r="F6" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>27</v>
@@ -2089,13 +2462,13 @@
         <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>192</v>
+      <c r="F7" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>27</v>
@@ -2109,13 +2482,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>189</v>
+      <c r="F8" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>27</v>
@@ -2132,13 +2505,13 @@
         <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>190</v>
+      <c r="F9" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>26</v>
@@ -2155,12 +2528,12 @@
         <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E10" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -2175,13 +2548,13 @@
         <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>191</v>
+        <v>164</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>37</v>
@@ -2198,13 +2571,13 @@
         <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>218</v>
+        <v>165</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>26</v>
@@ -2221,13 +2594,13 @@
         <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>220</v>
+        <v>166</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>179</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>27</v>
@@ -2244,13 +2617,13 @@
         <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>222</v>
+        <v>167</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>181</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>27</v>
@@ -2264,13 +2637,13 @@
         <v>58</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>224</v>
+        <v>160</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>183</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>27</v>
@@ -2287,13 +2660,13 @@
         <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>226</v>
+        <v>168</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>27</v>
@@ -2307,19 +2680,19 @@
         <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>228</v>
+        <v>169</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>187</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2332,11 +2705,11 @@
       <c r="D18" s="2">
         <v>2009</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>230</v>
+      <c r="E18" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>189</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>27</v>
@@ -2355,11 +2728,11 @@
       <c r="D19" s="2">
         <v>2007</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>231</v>
+      <c r="E19" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>27</v>
@@ -2376,13 +2749,13 @@
         <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>232</v>
+        <v>166</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>191</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>27</v>
@@ -2399,13 +2772,13 @@
         <v>64</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>235</v>
+        <v>160</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>27</v>
@@ -2419,25 +2792,25 @@
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>216</v>
+        <v>157</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2448,13 +2821,13 @@
         <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>241</v>
+        <v>197</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>26</v>
@@ -2468,13 +2841,13 @@
         <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>243</v>
+        <v>166</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>202</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>37</v>
@@ -2488,13 +2861,13 @@
         <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>245</v>
+        <v>198</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>27</v>
@@ -2514,13 +2887,13 @@
         <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>247</v>
+        <v>160</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>27</v>
@@ -2534,13 +2907,13 @@
         <v>70</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>268</v>
+        <v>168</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>27</v>
@@ -2554,19 +2927,19 @@
         <v>71</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>266</v>
+        <v>207</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2577,19 +2950,19 @@
         <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>264</v>
+        <v>208</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2600,13 +2973,13 @@
         <v>73</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>262</v>
+        <v>166</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>27</v>
@@ -2620,19 +2993,19 @@
         <v>74</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>260</v>
+        <v>166</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2643,19 +3016,19 @@
         <v>75</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>258</v>
+        <v>208</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2666,19 +3039,19 @@
         <v>76</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>256</v>
+        <v>157</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2689,16 +3062,16 @@
         <v>77</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>254</v>
+        <v>209</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2709,16 +3082,16 @@
         <v>78</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>252</v>
+        <v>210</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>211</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2729,13 +3102,13 @@
         <v>79</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>309</v>
+        <v>164</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>27</v>
@@ -2752,16 +3125,16 @@
         <v>80</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>307</v>
+        <v>232</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>261</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2772,16 +3145,16 @@
         <v>81</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>305</v>
+        <v>208</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2792,19 +3165,19 @@
         <v>82</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>303</v>
+        <v>233</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>257</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2815,16 +3188,16 @@
         <v>83</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>301</v>
+        <v>234</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>255</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2835,16 +3208,16 @@
         <v>84</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>299</v>
+        <v>235</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>253</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2855,13 +3228,13 @@
         <v>85</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>297</v>
+        <v>162</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>251</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>27</v>
@@ -2875,13 +3248,13 @@
         <v>86</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>295</v>
+        <v>167</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>27</v>
@@ -2895,13 +3268,13 @@
         <v>87</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>293</v>
+        <v>160</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>247</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>27</v>
@@ -2918,13 +3291,13 @@
         <v>88</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>291</v>
+        <v>207</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>245</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>27</v>
@@ -2938,13 +3311,13 @@
         <v>89</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>289</v>
+        <v>236</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>243</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>26</v>
@@ -2953,7 +3326,7 @@
         <v>27</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2964,13 +3337,13 @@
         <v>90</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>287</v>
+        <v>237</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>26</v>
@@ -2981,19 +3354,19 @@
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="D48" s="2">
         <v>2008</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>311</v>
+      <c r="E48" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>265</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>27</v>
@@ -3003,8 +3376,8 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="10"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
@@ -3017,13 +3390,13 @@
         <v>6</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>333</v>
+        <v>238</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>287</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>26</v>
@@ -3046,19 +3419,19 @@
         <v>8</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>331</v>
+        <v>159</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3069,16 +3442,16 @@
         <v>9</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>329</v>
+        <v>164</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>283</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,13 +3462,13 @@
         <v>10</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>327</v>
+        <v>160</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>281</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>26</v>
@@ -3115,13 +3488,13 @@
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>325</v>
+        <v>164</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>279</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>23</v>
@@ -3136,13 +3509,13 @@
         <v>31</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>323</v>
+        <v>157</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>23</v>
@@ -3157,13 +3530,13 @@
         <v>41</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>321</v>
+        <v>207</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>275</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>23</v>
@@ -3178,13 +3551,13 @@
         <v>42</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>319</v>
+        <v>239</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>26</v>
@@ -3199,16 +3572,16 @@
         <v>43</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>317</v>
+        <v>160</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>271</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3220,16 +3593,16 @@
         <v>44</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>315</v>
+        <v>240</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3241,638 +3614,1170 @@
         <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>313</v>
+        <v>157</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>267</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="9"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="10"/>
-    </row>
-    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" s="2">
-        <v>3</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B68" s="2">
-        <v>4</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-    </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B105" s="2">
-        <v>5</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="F114" s="12" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C2:C21 C50:C60 C62:C103 C105:C113 D2:D4 C23:C47" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:C21 C50:C60 D2:D4 C23:C47" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371D5FB7-89ED-7F46-8BAA-02CDBADA95C6}">
+  <dimension ref="A1:H73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" style="17" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="17"/>
+    <col min="3" max="3" width="7" style="17" customWidth="1"/>
+    <col min="4" max="4" width="73.1640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="17"/>
+    <col min="6" max="6" width="24.5" style="17" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="17" customWidth="1"/>
+    <col min="8" max="8" width="27.83203125" style="17" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="17">
+        <v>3</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="17">
+        <v>4</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="18"/>
+      <c r="D20" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="18"/>
+      <c r="D21" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="18"/>
+      <c r="D22" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="18"/>
+      <c r="D23" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="18"/>
+      <c r="D24" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="18"/>
+      <c r="D25" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E25" s="17">
+        <v>2021</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="18"/>
+      <c r="D26" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" s="17">
+        <v>2022</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="18"/>
+      <c r="D27" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="18"/>
+      <c r="D28" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="18"/>
+      <c r="D29" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="18"/>
+      <c r="D30" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="18"/>
+      <c r="D31" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="18"/>
+      <c r="D32" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="18"/>
+      <c r="D34" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="18"/>
+      <c r="D35" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="18"/>
+      <c r="D36" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="18"/>
+      <c r="D37" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="18"/>
+      <c r="D38" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="18"/>
+      <c r="D39" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="18"/>
+      <c r="D40" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="18"/>
+      <c r="D41" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="18"/>
+      <c r="D42" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="18"/>
+      <c r="D43" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="18"/>
+      <c r="D44" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="H44" s="19"/>
+    </row>
+    <row r="45" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="18"/>
+      <c r="D45" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="18"/>
+      <c r="D46" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="18"/>
+      <c r="D47" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="18"/>
+      <c r="D48" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="18"/>
+      <c r="D49" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="18"/>
+      <c r="D50" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="18"/>
+      <c r="D51" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="18"/>
+      <c r="D52" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="18"/>
+      <c r="D53" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="18"/>
+      <c r="D54" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="18"/>
+      <c r="D55" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="16"/>
+      <c r="E56" s="18"/>
+    </row>
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="17">
+        <v>5</v>
+      </c>
+      <c r="C57" s="18"/>
+      <c r="D57" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="E57" s="17">
+        <v>2021</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="18"/>
+      <c r="D58" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="E58" s="17">
+        <v>2024</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="18"/>
+      <c r="D59" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="18"/>
+      <c r="D60" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="18"/>
+      <c r="D61" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="18"/>
+      <c r="D62" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="18"/>
+      <c r="D63" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="18"/>
+      <c r="D64" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="18"/>
+      <c r="D65" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="18"/>
+      <c r="D66" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C67" s="18"/>
+      <c r="D67" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="18"/>
+      <c r="D68" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="18"/>
+      <c r="D69" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="18"/>
+      <c r="D70" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D71" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="H71" s="19" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D72" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D73" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D57:H72">
+    <sortCondition ref="E57:E72"/>
+  </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{32A3ED64-41C2-714A-8633-FA4F34409601}"/>
+    <hyperlink ref="H7" r:id="rId2" xr:uid="{2178E723-2F43-FA43-8EAE-E50AF0935AD1}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{F757DF57-CE17-0541-972E-961A394823CE}"/>
+    <hyperlink ref="H9" r:id="rId4" xr:uid="{F63495F3-EB02-1644-985D-398C3A08CAC5}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{BBED2221-5D01-B64F-83EA-1F03AE1B2F80}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{6D039BA1-3E98-B549-AA2F-C054278C9B43}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{D0C24E8F-5BC3-4840-B1D4-A2320537CFE7}"/>
+    <hyperlink ref="H13" r:id="rId8" xr:uid="{93305877-5D6A-664F-BF8E-6ABC6B1C01C0}"/>
+    <hyperlink ref="H14" r:id="rId9" xr:uid="{04F64F77-C4A1-044C-AF2E-4AF510C4D19A}"/>
+    <hyperlink ref="H5" r:id="rId10" xr:uid="{4E8FEF3B-F68D-214E-854A-4F6B4814611F}"/>
+    <hyperlink ref="H4" r:id="rId11" xr:uid="{E5798717-67C0-6C4B-95B2-B45E15B9E1E2}"/>
+    <hyperlink ref="H3" r:id="rId12" xr:uid="{36B9717A-4E40-E045-8B16-BD87E46F0D30}"/>
+    <hyperlink ref="H22" r:id="rId13" xr:uid="{C07F8C2A-8675-4847-8701-083D3D184AB3}"/>
+    <hyperlink ref="H26" r:id="rId14" xr:uid="{85CCFC19-F813-CF4A-82EF-CB817A51BAB0}"/>
+    <hyperlink ref="H27" r:id="rId15" xr:uid="{DBE1DAB6-3AF8-D941-983B-1599172BC3B5}"/>
+    <hyperlink ref="H28" r:id="rId16" xr:uid="{D2F96310-FEAF-4F4A-B215-5C5F8167FB30}"/>
+    <hyperlink ref="H29" r:id="rId17" xr:uid="{8CBC0899-518F-EE40-973F-F0F881939C69}"/>
+    <hyperlink ref="H40" r:id="rId18" xr:uid="{A5306D51-6A09-3143-99A9-6767A5656F82}"/>
+    <hyperlink ref="H42" r:id="rId19" xr:uid="{468F0601-28ED-944E-87AD-A325C04BEAD9}"/>
+    <hyperlink ref="H43" r:id="rId20" xr:uid="{F5A285F6-382D-7E44-8E2E-2150E2D376C7}"/>
+    <hyperlink ref="H52" r:id="rId21" xr:uid="{0D1867ED-84B8-9846-A330-5882413FD358}"/>
+    <hyperlink ref="H53" r:id="rId22" xr:uid="{4097BC5C-2CFE-194F-A59A-BFE763131D11}"/>
+    <hyperlink ref="H71" r:id="rId23" xr:uid="{2E953DBD-011F-FB4A-93C4-48A52FCF9AA1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B72D82-9823-C241-8645-4BCD8A0E8126}">
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/txt/giinhan txt.xlsx
+++ b/txt/giinhan txt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5BA44-820F-134F-A6B6-9AE9146F28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B9F97B-8655-604C-84C3-415373AEB424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="680" windowWidth="27140" windowHeight="19660" activeTab="1" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="6560" yWindow="680" windowWidth="27140" windowHeight="19660" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="467">
   <si>
     <t>category</t>
   </si>
@@ -133,15 +133,6 @@
     <t>designer</t>
   </si>
   <si>
-    <t>파타고니아 코리아
-환경 캠페인
-지천구곡:우리를 살게하는 강</t>
-  </si>
-  <si>
-    <t>아름답지만 피곤한
-남방큰돌고래</t>
-  </si>
-  <si>
     <t>artist</t>
   </si>
   <si>
@@ -157,15 +148,6 @@
 편집 &amp; 디자인 | 한지인 [ORB]</t>
   </si>
   <si>
-    <t>누구나 알기 쉬운 
-탄소중립 녹색성장 안내서</t>
-  </si>
-  <si>
-    <t>MARC 캠페인
-남방큰돌고래와 함께 살기
-&lt;적정거리를 지켜요 2&gt;</t>
-  </si>
-  <si>
     <t>MARC 바다거북 시민참여과학
 결과보고와 나름의 연말파티</t>
   </si>
@@ -480,24 +462,6 @@
     <t>도넛</t>
   </si>
   <si>
-    <t>손잡브</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>작브살</t>
-  </si>
-  <si>
-    <t>코리아나</t>
-  </si>
-  <si>
-    <t>제일기획</t>
-  </si>
-  <si>
-    <t>지큐</t>
-  </si>
-  <si>
     <t>비마이비</t>
   </si>
   <si>
@@ -505,9 +469,6 @@
   </si>
   <si>
     <t>넥스트로컬</t>
-  </si>
-  <si>
-    <t>춘천일기</t>
   </si>
   <si>
     <t>한국의서원</t>
@@ -640,9 +601,6 @@
   </si>
   <si>
     <t>갈닫사미페</t>
-  </si>
-  <si>
-    <t>관광두레 브랜딩 멘토</t>
   </si>
   <si>
     <t>갈다 사이언스 미디어 페스티벌 2025
@@ -1350,9 +1308,6 @@
     <t>https://www.koreana.or.kr/koreana/an/arn/selectArNttInfo.do?bbsId=1109&amp;nttSn=120484</t>
   </si>
   <si>
-    <t>매우 당연한 시장, 마르쉐 / Farmers Markets Sow Connections</t>
-  </si>
-  <si>
     <t>https://magazine.cheil.com/53115</t>
   </si>
   <si>
@@ -1407,9 +1362,6 @@
     <t>https://stonebc.com/archives/10789</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>https://product.kyobobook.co.kr/detail/S000214409291</t>
   </si>
   <si>
@@ -1434,9 +1386,6 @@
     <t>MKYU</t>
   </si>
   <si>
-    <t>2025 집중실험실</t>
-  </si>
-  <si>
     <t>MKYU 그린플루언서 자격증 과정</t>
   </si>
   <si>
@@ -1444,9 +1393,6 @@
   </si>
   <si>
     <t>서울예술대학교 시각디자인전공</t>
-  </si>
-  <si>
-    <t>브랜드 디자인</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=MUSuG1SeD2Q</t>
@@ -1729,15 +1675,9 @@
     <t>x</t>
   </si>
   <si>
-    <t>관광벤처기업 전문 컨설팅</t>
-  </si>
-  <si>
     <t>okus</t>
   </si>
   <si>
-    <t>창의적 먹거리경제조직 발굴 및 지원_3대가 협동조합 / 여성협동조합노둣돌</t>
-  </si>
-  <si>
     <t>한국의 서원 시행계획 수립 전략</t>
   </si>
   <si>
@@ -1745,9 +1685,6 @@
   </si>
   <si>
     <t>헤이그라운드 브랜딩 전략</t>
-  </si>
-  <si>
-    <t>드림위드 BEGIN AGAIN 멘토링 | 디아앤코</t>
   </si>
   <si>
     <t>한국문화예술교육진흥원 아르떼 아카데미</t>
@@ -1778,9 +1715,6 @@
     <t>루트임팩트 임팩트 캠퍼스 리브랜딩</t>
   </si>
   <si>
-    <t>임팩트 프랜차이즈 브랜딩 멘토링 | 알키 / 와로</t>
-  </si>
-  <si>
     <t>서울환경연합 브랜딩 전략</t>
   </si>
   <si>
@@ -1815,6 +1749,132 @@
   </si>
   <si>
     <t>2022 서울 로컬브랜드 상권조성 프로젝트 브랜딩 액션러닝 코치</t>
+  </si>
+  <si>
+    <t>매우 당연한 시장, 마르쉐 [KR]
+/ Farmers Markets Sow Connections [EN]</t>
+  </si>
+  <si>
+    <t>2025 집중실험실 [공통 교육]</t>
+  </si>
+  <si>
+    <t>https://seoulpa.kr/home/kor/M734735249/center/business/view.do?idx=cb00d1a0008a85e71a41b8741facbffea2efa7377741dc1594eb998bdc6687b4&amp;eSearchValue1=&amp;searchValue2=&amp;searchValue3=0&amp;searchKeyword=%5B2025+집중실험실%5D+공통교육&amp;searchValue10=B&amp;pageIndex=1</t>
+  </si>
+  <si>
+    <t>https://seoulpa.kr/home/kor/M734735249/center/business/view.do?idx=cb00d1a0008a85e71a41b8741facbffe8f0577f797597310562a1ed20b5a23d9&amp;eSearchValue1=&amp;searchValue2=&amp;searchValue3=0&amp;searchKeyword=%5B2025+집중실험실%5D+공통교육&amp;searchValue10=B&amp;pageIndex=1</t>
+  </si>
+  <si>
+    <t>https://seoulpa.kr/home/kor/M734735249/center/business/view.do?idx=cb00d1a0008a85e71a41b8741facbffe95b67a336cef5c7f1844f4aac5baa10f&amp;eSearchValue1=&amp;searchValue2=&amp;searchValue3=0&amp;searchKeyword=%5B2025+집중실험실%5D+공통교육&amp;searchValue10=B&amp;pageIndex=1</t>
+  </si>
+  <si>
+    <t>2회차</t>
+  </si>
+  <si>
+    <t>3회차</t>
+  </si>
+  <si>
+    <t>후기 1회차</t>
+  </si>
+  <si>
+    <t>브랜드 디자인 1/2 [전공 교과목]</t>
+  </si>
+  <si>
+    <t>*영리기반 개인/기업 컨설팅 내역은 사이트에서 공개하지 않습니다. 궁금한 내용은 별도로 물어봐주세요.</t>
+  </si>
+  <si>
+    <t>관광두레 전문가 멘토링 | 브랜딩 분야</t>
+  </si>
+  <si>
+    <t>드림위드 BEGIN AGAIN 멘토링</t>
+  </si>
+  <si>
+    <t>임팩트 프랜차이즈 브랜딩 멘토링</t>
+  </si>
+  <si>
+    <t>창의적 먹거리경제조직 발굴 및 지원</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>PM/F&amp;B</t>
+  </si>
+  <si>
+    <t>manager/PR</t>
+  </si>
+  <si>
+    <t>c.director</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>이야기 지도
+주문진 수산시장</t>
+  </si>
+  <si>
+    <t>다채롭고 풍부한 자연산 어종을 철마다 선보이는 강릉시 주문진수산시장의 시장 활성화 사업의 일환으로 시장을 둘러싼 로컬 컨텐츠를 지도의 형식으로 디자인, 제작했습니다. 
+여행자와 주민 모두에게 필요한 주요 정보를 한 장에 담아 정말 유용하면서도 말랑말랑한 이야기를 전달합니다.
+기획 진행 | 감자꽃 스튜디오
+그래픽 | 한지인</t>
+  </si>
+  <si>
+    <t>망안한 사진대회
+동물권행동 카라 온라인 캠페인</t>
+  </si>
+  <si>
+    <t>동물권행동 카라가 2020년 미디어 속 동물의 안전과 권리를 위해 제작한 국내 최초의 동물 출연 미디어 가이드라인의 버벌브랜딩과 에디터 작업으로 함께 준비하면서, 동물들의 ‘대상화되지 않은 동물 이미지’를 환호하기 위해 만들어진 캠페인입니다.
+동물의 본능이 느껴지는 날 것의 이미지를 수집하기 위해 카라, 오늘의풍경과 함께 기획하고 네이밍과 컨텐츠 라이팅의 업무를 진행했습니다.
+했습니다. 카라 가이드라인은 국내 제작사들에게 배포, 활용되고 있으며 국내 방송사가 동물 출연 조항 및 가이드라인을 신설하는 것에 기여하였습니다.
+참가자 컬렉션 #망안한사진대회 #카라동물미디어가이드라인 
+https://www.instagram.com/explore/search/keyword/?q=%23망안한사진대회
+디자인 스튜디오 오늘의 풍경의 프로젝트 후기
+https://blog.sceneryoftoday.kr/animal-in-media/
+기획 | 동물권행동 카라, 오늘의풍경, 한지인
+디자인 | 오늘의풍경
+버벌 브랜딩 | 한지인</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>프리랜서 디자이너의 삶</t>
+  </si>
+  <si>
+    <t>홍익대학교 시각디자인전공</t>
+  </si>
+  <si>
+    <t>디자인 스타트업 패키지 1:1 멘토링</t>
+  </si>
+  <si>
+    <t>서울문화재단 CoP 2025 주니어보드</t>
+  </si>
+  <si>
+    <t>https://www.mkyu.co.kr/course/course_view.jsp?id=157340&amp;cid=#course-view-157340</t>
+  </si>
+  <si>
+    <t>관련 링크</t>
+  </si>
+  <si>
+    <t>아름답지만 피곤한 남방큰돌고래
+해양동물생태연구소 마크 생태 전시</t>
+  </si>
+  <si>
+    <t>지천구곡:우리를 살게하는 강
+파타고니아 코리아 환경 캠페인</t>
+  </si>
+  <si>
+    <t>누구나 알기 쉬운 탄소중립 녹색성장 안내서</t>
+  </si>
+  <si>
+    <t>적정거리를 지켜요 2
+MARC 캠페인 - 남방큰돌고래와 함께 살기</t>
   </si>
 </sst>
 </file>
@@ -2294,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
@@ -2315,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>16</v>
@@ -2335,7 +2395,7 @@
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -2344,13 +2404,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>28</v>
+        <v>464</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>22</v>
@@ -2364,7 +2424,7 @@
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -2373,7 +2433,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>25</v>
@@ -2382,7 +2442,7 @@
         <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>27</v>
@@ -2390,19 +2450,19 @@
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>33</v>
+        <v>465</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
@@ -2413,42 +2473,42 @@
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>29</v>
+        <v>463</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>27</v>
@@ -2456,19 +2516,19 @@
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>34</v>
+        <v>466</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>27</v>
@@ -2476,45 +2536,45 @@
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>26</v>
+        <v>446</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>27</v>
@@ -2522,19 +2582,19 @@
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>27</v>
@@ -2542,22 +2602,22 @@
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>21</v>
@@ -2565,65 +2625,65 @@
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>27</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>178</v>
-      </c>
       <c r="F13" s="11" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>27</v>
@@ -2631,42 +2691,42 @@
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>27</v>
@@ -2674,206 +2734,206 @@
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2">
         <v>2009</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2">
         <v>2007</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>26</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>23</v>
@@ -2881,19 +2941,19 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>27</v>
@@ -2901,19 +2961,19 @@
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>27</v>
@@ -2921,65 +2981,65 @@
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>27</v>
@@ -2987,254 +3047,254 @@
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>27</v>
@@ -3242,19 +3302,19 @@
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>27</v>
@@ -3262,42 +3322,42 @@
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>27</v>
@@ -3305,19 +3365,19 @@
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>26</v>
@@ -3326,24 +3386,24 @@
         <v>27</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>26</v>
@@ -3354,278 +3414,328 @@
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D48" s="2">
         <v>2008</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
+      <c r="C49" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2010</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="2">
-        <v>2</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>238</v>
+        <v>455</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2020</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>288</v>
+        <v>453</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>287</v>
+        <v>454</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>289</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>289</v>
-      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="10"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C55" s="3" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>278</v>
+        <v>148</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="F55" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B56" s="4"/>
+      <c r="A56" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="C56" s="3" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>23</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="4"/>
+        <v>126</v>
+      </c>
       <c r="C57" s="3" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="H57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B58" s="4"/>
+        <v>127</v>
+      </c>
       <c r="C58" s="3" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>231</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>270</v>
+        <v>146</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>266</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>290</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>136</v>
+      <c r="A60" s="2">
+        <v>1010</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="3" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="H60" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3633,1147 +3743,1087 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C2:C21 C50:C60 D2:D4 C23:C47" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:C21 C54:C64 D2:D4 C23:C47" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371D5FB7-89ED-7F46-8BAA-02CDBADA95C6}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" style="17" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="17"/>
-    <col min="3" max="3" width="7" style="17" customWidth="1"/>
-    <col min="4" max="4" width="73.1640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="17"/>
-    <col min="6" max="6" width="24.5" style="17" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="27.83203125" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="17"/>
+    <col min="1" max="1" width="10.83203125" style="17"/>
+    <col min="2" max="2" width="73.1640625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="17"/>
+    <col min="4" max="4" width="24.5" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" style="17" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13"/>
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="13" t="s">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>400</v>
+        <v>405</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>283</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="17">
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17">
         <v>3</v>
       </c>
+      <c r="B3" s="17" t="s">
+        <v>280</v>
+      </c>
       <c r="C3" s="18" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D3" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="C7" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="C10" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="E10" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="17" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="17" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H7" s="20" t="s">
+      <c r="E13" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="17" t="s">
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="17" t="s">
+      <c r="C14" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17">
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="17">
         <v>4</v>
       </c>
+      <c r="B16" s="17" t="s">
+        <v>388</v>
+      </c>
       <c r="C16" s="18" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="18"/>
+      <c r="E21" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="18"/>
+      <c r="E22" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="17" t="s">
+      <c r="C47" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="17" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="17" t="s">
+      <c r="C57" s="17">
+        <v>2022</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F57" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="18"/>
-      <c r="D20" s="17" t="s">
-        <v>333</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="18"/>
-      <c r="D21" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C22" s="18"/>
-      <c r="D22" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="18"/>
-      <c r="D23" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F23" s="17" t="s">
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="17" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="18"/>
-      <c r="D24" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="18"/>
-      <c r="D25" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="E25" s="17">
+      <c r="C58" s="17">
         <v>2021</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="18"/>
-      <c r="D26" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="E26" s="17">
-        <v>2022</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="18"/>
-      <c r="D27" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C28" s="18"/>
-      <c r="D28" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="18"/>
-      <c r="D29" s="17" t="s">
+      <c r="D58" s="17" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="15"/>
+      <c r="C59" s="18"/>
+    </row>
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="17">
+        <v>5</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="C60" s="18"/>
+    </row>
+    <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="C77" s="17">
+        <v>2024</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="C78" s="17">
+        <v>2021</v>
+      </c>
+      <c r="D78" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C30" s="18"/>
-      <c r="D30" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="18"/>
-      <c r="D31" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="18"/>
-      <c r="D32" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="18"/>
-      <c r="D34" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="18"/>
-      <c r="D35" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="18"/>
-      <c r="D36" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="37" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="18"/>
-      <c r="D37" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="18"/>
-      <c r="D38" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="39" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="18"/>
-      <c r="D39" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="18"/>
-      <c r="D40" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="18"/>
-      <c r="D41" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="18"/>
-      <c r="D42" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="18"/>
-      <c r="D43" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="18"/>
-      <c r="D44" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="18"/>
-      <c r="D45" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="46" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="18"/>
-      <c r="D46" s="17" t="s">
-        <v>382</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="47" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="18"/>
-      <c r="D47" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="48" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="18"/>
-      <c r="D48" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="18"/>
-      <c r="D49" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="18"/>
-      <c r="D50" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="18"/>
-      <c r="D51" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="18"/>
-      <c r="D52" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="18"/>
-      <c r="D53" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="G53" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="18"/>
-      <c r="D54" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="18"/>
-      <c r="D55" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="16"/>
-      <c r="E56" s="18"/>
-    </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="17">
-        <v>5</v>
-      </c>
-      <c r="C57" s="18"/>
-      <c r="D57" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="E57" s="17">
-        <v>2021</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="18"/>
-      <c r="D58" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="E58" s="17">
-        <v>2024</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="18"/>
-      <c r="D59" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C60" s="18"/>
-      <c r="D60" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C61" s="18"/>
-      <c r="D61" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F61" s="17" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C62" s="18"/>
-      <c r="D62" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C63" s="18"/>
-      <c r="D63" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C64" s="18"/>
-      <c r="D64" s="17" t="s">
-        <v>430</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="65" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C65" s="18"/>
-      <c r="D65" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="66" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C66" s="18"/>
-      <c r="D66" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="67" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C67" s="18"/>
-      <c r="D67" s="17" t="s">
-        <v>449</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="68" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C68" s="18"/>
-      <c r="D68" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="69" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C69" s="18"/>
-      <c r="D69" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C70" s="18"/>
-      <c r="D70" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="71" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D71" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="G71" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="72" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D72" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="73" spans="3:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D73" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>402</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D57:H72">
-    <sortCondition ref="E57:E72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B61:F78">
+    <sortCondition descending="1" ref="C61:C78"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H6" r:id="rId1" xr:uid="{32A3ED64-41C2-714A-8633-FA4F34409601}"/>
-    <hyperlink ref="H7" r:id="rId2" xr:uid="{2178E723-2F43-FA43-8EAE-E50AF0935AD1}"/>
-    <hyperlink ref="H8" r:id="rId3" xr:uid="{F757DF57-CE17-0541-972E-961A394823CE}"/>
-    <hyperlink ref="H9" r:id="rId4" xr:uid="{F63495F3-EB02-1644-985D-398C3A08CAC5}"/>
-    <hyperlink ref="H10" r:id="rId5" xr:uid="{BBED2221-5D01-B64F-83EA-1F03AE1B2F80}"/>
-    <hyperlink ref="H11" r:id="rId6" xr:uid="{6D039BA1-3E98-B549-AA2F-C054278C9B43}"/>
-    <hyperlink ref="H12" r:id="rId7" xr:uid="{D0C24E8F-5BC3-4840-B1D4-A2320537CFE7}"/>
-    <hyperlink ref="H13" r:id="rId8" xr:uid="{93305877-5D6A-664F-BF8E-6ABC6B1C01C0}"/>
-    <hyperlink ref="H14" r:id="rId9" xr:uid="{04F64F77-C4A1-044C-AF2E-4AF510C4D19A}"/>
-    <hyperlink ref="H5" r:id="rId10" xr:uid="{4E8FEF3B-F68D-214E-854A-4F6B4814611F}"/>
-    <hyperlink ref="H4" r:id="rId11" xr:uid="{E5798717-67C0-6C4B-95B2-B45E15B9E1E2}"/>
-    <hyperlink ref="H3" r:id="rId12" xr:uid="{36B9717A-4E40-E045-8B16-BD87E46F0D30}"/>
-    <hyperlink ref="H22" r:id="rId13" xr:uid="{C07F8C2A-8675-4847-8701-083D3D184AB3}"/>
-    <hyperlink ref="H26" r:id="rId14" xr:uid="{85CCFC19-F813-CF4A-82EF-CB817A51BAB0}"/>
-    <hyperlink ref="H27" r:id="rId15" xr:uid="{DBE1DAB6-3AF8-D941-983B-1599172BC3B5}"/>
-    <hyperlink ref="H28" r:id="rId16" xr:uid="{D2F96310-FEAF-4F4A-B215-5C5F8167FB30}"/>
-    <hyperlink ref="H29" r:id="rId17" xr:uid="{8CBC0899-518F-EE40-973F-F0F881939C69}"/>
-    <hyperlink ref="H40" r:id="rId18" xr:uid="{A5306D51-6A09-3143-99A9-6767A5656F82}"/>
-    <hyperlink ref="H42" r:id="rId19" xr:uid="{468F0601-28ED-944E-87AD-A325C04BEAD9}"/>
-    <hyperlink ref="H43" r:id="rId20" xr:uid="{F5A285F6-382D-7E44-8E2E-2150E2D376C7}"/>
-    <hyperlink ref="H52" r:id="rId21" xr:uid="{0D1867ED-84B8-9846-A330-5882413FD358}"/>
-    <hyperlink ref="H53" r:id="rId22" xr:uid="{4097BC5C-2CFE-194F-A59A-BFE763131D11}"/>
-    <hyperlink ref="H71" r:id="rId23" xr:uid="{2E953DBD-011F-FB4A-93C4-48A52FCF9AA1}"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{32A3ED64-41C2-714A-8633-FA4F34409601}"/>
+    <hyperlink ref="F12" r:id="rId2" xr:uid="{2178E723-2F43-FA43-8EAE-E50AF0935AD1}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{F757DF57-CE17-0541-972E-961A394823CE}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{F63495F3-EB02-1644-985D-398C3A08CAC5}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{BBED2221-5D01-B64F-83EA-1F03AE1B2F80}"/>
+    <hyperlink ref="F9" r:id="rId6" xr:uid="{6D039BA1-3E98-B549-AA2F-C054278C9B43}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{D0C24E8F-5BC3-4840-B1D4-A2320537CFE7}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{93305877-5D6A-664F-BF8E-6ABC6B1C01C0}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{04F64F77-C4A1-044C-AF2E-4AF510C4D19A}"/>
+    <hyperlink ref="F5" r:id="rId10" xr:uid="{4E8FEF3B-F68D-214E-854A-4F6B4814611F}"/>
+    <hyperlink ref="F4" r:id="rId11" xr:uid="{E5798717-67C0-6C4B-95B2-B45E15B9E1E2}"/>
+    <hyperlink ref="F3" r:id="rId12" xr:uid="{36B9717A-4E40-E045-8B16-BD87E46F0D30}"/>
+    <hyperlink ref="F55" r:id="rId13" xr:uid="{C07F8C2A-8675-4847-8701-083D3D184AB3}"/>
+    <hyperlink ref="F57" r:id="rId14" xr:uid="{85CCFC19-F813-CF4A-82EF-CB817A51BAB0}"/>
+    <hyperlink ref="F42" r:id="rId15" xr:uid="{DBE1DAB6-3AF8-D941-983B-1599172BC3B5}"/>
+    <hyperlink ref="F43" r:id="rId16" xr:uid="{D2F96310-FEAF-4F4A-B215-5C5F8167FB30}"/>
+    <hyperlink ref="F44" r:id="rId17" xr:uid="{8CBC0899-518F-EE40-973F-F0F881939C69}"/>
+    <hyperlink ref="F36" r:id="rId18" xr:uid="{A5306D51-6A09-3143-99A9-6767A5656F82}"/>
+    <hyperlink ref="F38" r:id="rId19" xr:uid="{468F0601-28ED-944E-87AD-A325C04BEAD9}"/>
+    <hyperlink ref="F39" r:id="rId20" xr:uid="{F5A285F6-382D-7E44-8E2E-2150E2D376C7}"/>
+    <hyperlink ref="F29" r:id="rId21" xr:uid="{0D1867ED-84B8-9846-A330-5882413FD358}"/>
+    <hyperlink ref="F30" r:id="rId22" xr:uid="{4097BC5C-2CFE-194F-A59A-BFE763131D11}"/>
+    <hyperlink ref="F64" r:id="rId23" xr:uid="{2E953DBD-011F-FB4A-93C4-48A52FCF9AA1}"/>
+    <hyperlink ref="F20" r:id="rId24" xr:uid="{A5A3EA2C-66E5-6E4C-A151-23361DFF53A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="C70:C75 C35:C59 C61:C65 C3:C33 C67:C68" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
